--- a/AAII_Financials/Yearly/KUBTY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KUBTY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>KUBTY</t>
   </si>
@@ -656,196 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42094</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41729</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41364</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40999</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>17787000</v>
+        <v>20359600</v>
       </c>
       <c r="E8" s="3">
-        <v>14586500</v>
+        <v>18042800</v>
       </c>
       <c r="F8" s="3">
-        <v>12305500</v>
+        <v>14806200</v>
       </c>
       <c r="G8" s="3">
-        <v>12749100</v>
+        <v>12490800</v>
       </c>
       <c r="H8" s="3">
-        <v>12286100</v>
+        <v>12941100</v>
       </c>
       <c r="I8" s="3">
-        <v>11626900</v>
+        <v>12471100</v>
       </c>
       <c r="J8" s="3">
+        <v>11802000</v>
+      </c>
+      <c r="K8" s="3">
         <v>10598000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8825500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13980900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14497500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10613700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8941100</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>13162100</v>
+        <v>14452200</v>
       </c>
       <c r="E9" s="3">
-        <v>10391300</v>
+        <v>13421400</v>
       </c>
       <c r="F9" s="3">
-        <v>8754100</v>
+        <v>10547800</v>
       </c>
       <c r="G9" s="3">
-        <v>9031200</v>
+        <v>8885900</v>
       </c>
       <c r="H9" s="3">
-        <v>8784300</v>
+        <v>9167200</v>
       </c>
       <c r="I9" s="3">
-        <v>16462300</v>
+        <v>8916500</v>
       </c>
       <c r="J9" s="3">
+        <v>16710200</v>
+      </c>
+      <c r="K9" s="3">
         <v>7453700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6015100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9732900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10157800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7709700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6526900</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4624900</v>
+        <v>5907400</v>
       </c>
       <c r="E10" s="3">
-        <v>4195200</v>
+        <v>4621500</v>
       </c>
       <c r="F10" s="3">
-        <v>3551400</v>
+        <v>4258400</v>
       </c>
       <c r="G10" s="3">
-        <v>3717900</v>
+        <v>3604900</v>
       </c>
       <c r="H10" s="3">
-        <v>3501800</v>
+        <v>3773900</v>
       </c>
       <c r="I10" s="3">
-        <v>-4835400</v>
+        <v>3554600</v>
       </c>
       <c r="J10" s="3">
+        <v>-4908200</v>
+      </c>
+      <c r="K10" s="3">
         <v>3144300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2810300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4248000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4339800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2904100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2414300</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -862,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,51 +961,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>12900</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
-        <v>3800</v>
+        <v>13100</v>
       </c>
       <c r="F14" s="3">
-        <v>-9400</v>
+        <v>3900</v>
       </c>
       <c r="G14" s="3">
-        <v>-8700</v>
+        <v>-9500</v>
       </c>
       <c r="H14" s="3">
-        <v>-13300</v>
+        <v>-8900</v>
       </c>
       <c r="I14" s="3">
-        <v>5900</v>
+        <v>-13500</v>
       </c>
       <c r="J14" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K14" s="3">
         <v>1300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>31900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-6500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>15600</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>22800</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1026,12 +1048,15 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>16333300</v>
+        <v>18143300</v>
       </c>
       <c r="E17" s="3">
-        <v>12962600</v>
+        <v>16597900</v>
       </c>
       <c r="F17" s="3">
-        <v>11141600</v>
+        <v>13157800</v>
       </c>
       <c r="G17" s="3">
-        <v>11410100</v>
+        <v>11309400</v>
       </c>
       <c r="H17" s="3">
-        <v>11029100</v>
+        <v>11581900</v>
       </c>
       <c r="I17" s="3">
-        <v>10299200</v>
+        <v>11195200</v>
       </c>
       <c r="J17" s="3">
+        <v>10454300</v>
+      </c>
+      <c r="K17" s="3">
         <v>9344600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7642300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12182400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12552200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9585100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8026500</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1453800</v>
+        <v>2216300</v>
       </c>
       <c r="E18" s="3">
-        <v>1623900</v>
+        <v>1445000</v>
       </c>
       <c r="F18" s="3">
-        <v>1163900</v>
+        <v>1648400</v>
       </c>
       <c r="G18" s="3">
-        <v>1339000</v>
+        <v>1181400</v>
       </c>
       <c r="H18" s="3">
-        <v>1257000</v>
+        <v>1359100</v>
       </c>
       <c r="I18" s="3">
-        <v>1327700</v>
+        <v>1276000</v>
       </c>
       <c r="J18" s="3">
+        <v>1347700</v>
+      </c>
+      <c r="K18" s="3">
         <v>1253500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1183100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1798500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1945400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1028600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>914600</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,218 +1179,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>110100</v>
+        <v>90700</v>
       </c>
       <c r="E20" s="3">
-        <v>48800</v>
+        <v>123800</v>
       </c>
       <c r="F20" s="3">
-        <v>77400</v>
+        <v>49500</v>
       </c>
       <c r="G20" s="3">
-        <v>55900</v>
+        <v>78500</v>
       </c>
       <c r="H20" s="3">
-        <v>59500</v>
+        <v>56800</v>
       </c>
       <c r="I20" s="3">
-        <v>99400</v>
+        <v>60400</v>
       </c>
       <c r="J20" s="3">
+        <v>100900</v>
+      </c>
+      <c r="K20" s="3">
         <v>57700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>23600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>73100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>99600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>78000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2500</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2127200</v>
+        <v>3033200</v>
       </c>
       <c r="E21" s="3">
-        <v>2146600</v>
+        <v>2145600</v>
       </c>
       <c r="F21" s="3">
-        <v>1686400</v>
+        <v>2183300</v>
       </c>
       <c r="G21" s="3">
-        <v>1806300</v>
+        <v>1715800</v>
       </c>
       <c r="H21" s="3">
-        <v>1644500</v>
+        <v>1837300</v>
       </c>
       <c r="I21" s="3">
-        <v>1725400</v>
+        <v>1672300</v>
       </c>
       <c r="J21" s="3">
+        <v>1754200</v>
+      </c>
+      <c r="K21" s="3">
         <v>1597900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1419800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2209300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2383900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1373100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1124200</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>10600</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E22" s="3">
-        <v>6600</v>
+        <v>10800</v>
       </c>
       <c r="F22" s="3">
-        <v>6900</v>
+        <v>6700</v>
       </c>
       <c r="G22" s="3">
         <v>7000</v>
       </c>
       <c r="H22" s="3">
-        <v>6900</v>
+        <v>7100</v>
       </c>
       <c r="I22" s="3">
-        <v>6100</v>
+        <v>7000</v>
       </c>
       <c r="J22" s="3">
+        <v>6200</v>
+      </c>
+      <c r="K22" s="3">
         <v>3300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>10400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>16800</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1553300</v>
+        <v>2307000</v>
       </c>
       <c r="E23" s="3">
-        <v>1666100</v>
+        <v>1558000</v>
       </c>
       <c r="F23" s="3">
-        <v>1234400</v>
+        <v>1691200</v>
       </c>
       <c r="G23" s="3">
-        <v>1387900</v>
+        <v>1253000</v>
       </c>
       <c r="H23" s="3">
-        <v>1309600</v>
+        <v>1408800</v>
       </c>
       <c r="I23" s="3">
-        <v>1421000</v>
+        <v>1329300</v>
       </c>
       <c r="J23" s="3">
+        <v>1442400</v>
+      </c>
+      <c r="K23" s="3">
         <v>1307900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1201800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1861200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2030500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1095000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>895300</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>392700</v>
+        <v>568900</v>
       </c>
       <c r="E24" s="3">
-        <v>430000</v>
+        <v>393300</v>
       </c>
       <c r="F24" s="3">
-        <v>312300</v>
+        <v>436500</v>
       </c>
       <c r="G24" s="3">
-        <v>351900</v>
+        <v>317000</v>
       </c>
       <c r="H24" s="3">
-        <v>326200</v>
+        <v>357200</v>
       </c>
       <c r="I24" s="3">
-        <v>416700</v>
+        <v>331100</v>
       </c>
       <c r="J24" s="3">
+        <v>423000</v>
+      </c>
+      <c r="K24" s="3">
         <v>375500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>384700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>539200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>691100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>370300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>324200</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1160500</v>
+        <v>1738200</v>
       </c>
       <c r="E26" s="3">
-        <v>1236100</v>
+        <v>1164700</v>
       </c>
       <c r="F26" s="3">
-        <v>922100</v>
+        <v>1254700</v>
       </c>
       <c r="G26" s="3">
-        <v>1036000</v>
+        <v>936000</v>
       </c>
       <c r="H26" s="3">
-        <v>983500</v>
+        <v>1051600</v>
       </c>
       <c r="I26" s="3">
-        <v>1004300</v>
+        <v>998300</v>
       </c>
       <c r="J26" s="3">
+        <v>1019400</v>
+      </c>
+      <c r="K26" s="3">
         <v>932400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>817100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1322000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1339400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>724700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>571100</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1037000</v>
+        <v>1607200</v>
       </c>
       <c r="E27" s="3">
-        <v>1180600</v>
+        <v>1054600</v>
       </c>
       <c r="F27" s="3">
-        <v>853400</v>
+        <v>1198400</v>
       </c>
       <c r="G27" s="3">
-        <v>989700</v>
+        <v>866200</v>
       </c>
       <c r="H27" s="3">
-        <v>920300</v>
+        <v>1004700</v>
       </c>
       <c r="I27" s="3">
-        <v>916600</v>
+        <v>934100</v>
       </c>
       <c r="J27" s="3">
+        <v>930400</v>
+      </c>
+      <c r="K27" s="3">
         <v>879700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>780700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1233500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1265300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>669800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>546000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1545,11 +1605,11 @@
       <c r="H29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="3">
-        <v>-69200</v>
-      </c>
-      <c r="J29" s="3" t="s">
+      <c r="I29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-70200</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-110100</v>
+        <v>-90700</v>
       </c>
       <c r="E32" s="3">
-        <v>-48800</v>
+        <v>-123800</v>
       </c>
       <c r="F32" s="3">
-        <v>-77400</v>
+        <v>-49500</v>
       </c>
       <c r="G32" s="3">
-        <v>-55900</v>
+        <v>-78500</v>
       </c>
       <c r="H32" s="3">
-        <v>-59500</v>
+        <v>-56800</v>
       </c>
       <c r="I32" s="3">
-        <v>-99400</v>
+        <v>-60400</v>
       </c>
       <c r="J32" s="3">
+        <v>-100900</v>
+      </c>
+      <c r="K32" s="3">
         <v>-57700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-23600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-73100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-99600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-78000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2500</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1037000</v>
+        <v>1607200</v>
       </c>
       <c r="E33" s="3">
-        <v>1180600</v>
+        <v>1054600</v>
       </c>
       <c r="F33" s="3">
-        <v>853400</v>
+        <v>1198400</v>
       </c>
       <c r="G33" s="3">
-        <v>989700</v>
+        <v>866200</v>
       </c>
       <c r="H33" s="3">
-        <v>920300</v>
+        <v>1004700</v>
       </c>
       <c r="I33" s="3">
-        <v>847400</v>
+        <v>934100</v>
       </c>
       <c r="J33" s="3">
+        <v>860200</v>
+      </c>
+      <c r="K33" s="3">
         <v>879700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>780700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1233500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1265300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>669800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>546000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1037000</v>
+        <v>1607200</v>
       </c>
       <c r="E35" s="3">
-        <v>1180600</v>
+        <v>1054600</v>
       </c>
       <c r="F35" s="3">
-        <v>853400</v>
+        <v>1198400</v>
       </c>
       <c r="G35" s="3">
-        <v>989700</v>
+        <v>866200</v>
       </c>
       <c r="H35" s="3">
-        <v>920300</v>
+        <v>1004700</v>
       </c>
       <c r="I35" s="3">
-        <v>847400</v>
+        <v>934100</v>
       </c>
       <c r="J35" s="3">
+        <v>860200</v>
+      </c>
+      <c r="K35" s="3">
         <v>879700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>780700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1233500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1265300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>669800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>546000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42094</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41729</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41364</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40999</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,386 +1987,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2703900</v>
+        <v>1497100</v>
       </c>
       <c r="E41" s="3">
-        <v>3096400</v>
+        <v>2744700</v>
       </c>
       <c r="F41" s="3">
-        <v>1480200</v>
+        <v>3143000</v>
       </c>
       <c r="G41" s="3">
-        <v>1325800</v>
+        <v>1502500</v>
       </c>
       <c r="H41" s="3">
-        <v>1521400</v>
+        <v>1345700</v>
       </c>
       <c r="I41" s="3">
-        <v>3064000</v>
+        <v>1544300</v>
       </c>
       <c r="J41" s="3">
+        <v>3110100</v>
+      </c>
+      <c r="K41" s="3">
         <v>1124900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1037200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>995700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>836300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1004800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>892000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>769500</v>
+        <v>559500</v>
       </c>
       <c r="E42" s="3">
-        <v>676200</v>
+        <v>781100</v>
       </c>
       <c r="F42" s="3">
-        <v>331800</v>
+        <v>686400</v>
       </c>
       <c r="G42" s="3">
-        <v>477900</v>
+        <v>336800</v>
       </c>
       <c r="H42" s="3">
-        <v>361000</v>
+        <v>485100</v>
       </c>
       <c r="I42" s="3">
-        <v>353800</v>
+        <v>366500</v>
       </c>
       <c r="J42" s="3">
+        <v>359100</v>
+      </c>
+      <c r="K42" s="3">
         <v>40500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>53800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>80100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>44500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>38800</v>
       </c>
-      <c r="O42" s="3" t="s">
+      <c r="P42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>13745800</v>
+        <v>10456000</v>
       </c>
       <c r="E43" s="3">
-        <v>6565100</v>
+        <v>13952900</v>
       </c>
       <c r="F43" s="3">
-        <v>6104500</v>
+        <v>6664000</v>
       </c>
       <c r="G43" s="3">
-        <v>6525900</v>
+        <v>6196400</v>
       </c>
       <c r="H43" s="3">
-        <v>6189000</v>
+        <v>6624200</v>
       </c>
       <c r="I43" s="3">
-        <v>16351300</v>
+        <v>6282200</v>
       </c>
       <c r="J43" s="3">
+        <v>16597600</v>
+      </c>
+      <c r="K43" s="3">
         <v>5823300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6038400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7816300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7348700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5510400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4425400</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>8558600</v>
+        <v>4502600</v>
       </c>
       <c r="E44" s="3">
-        <v>3386800</v>
+        <v>8687500</v>
       </c>
       <c r="F44" s="3">
-        <v>2483300</v>
+        <v>3437800</v>
       </c>
       <c r="G44" s="3">
-        <v>2539100</v>
+        <v>2520700</v>
       </c>
       <c r="H44" s="3">
-        <v>2461400</v>
+        <v>2577400</v>
       </c>
       <c r="I44" s="3">
-        <v>4789900</v>
+        <v>2498500</v>
       </c>
       <c r="J44" s="3">
+        <v>4862000</v>
+      </c>
+      <c r="K44" s="3">
         <v>2365000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5054300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2978100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2880700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2104200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1792400</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>366700</v>
+        <v>376400</v>
       </c>
       <c r="E45" s="3">
-        <v>392500</v>
+        <v>372200</v>
       </c>
       <c r="F45" s="3">
-        <v>480100</v>
+        <v>398400</v>
       </c>
       <c r="G45" s="3">
-        <v>544700</v>
+        <v>487300</v>
       </c>
       <c r="H45" s="3">
-        <v>353600</v>
+        <v>552900</v>
       </c>
       <c r="I45" s="3">
-        <v>1091600</v>
+        <v>358900</v>
       </c>
       <c r="J45" s="3">
+        <v>1108000</v>
+      </c>
+      <c r="K45" s="3">
         <v>1025100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1880900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>842800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>748200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>565200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>571800</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>15190900</v>
+        <v>17391700</v>
       </c>
       <c r="E46" s="3">
-        <v>12399600</v>
+        <v>15419600</v>
       </c>
       <c r="F46" s="3">
-        <v>10879900</v>
+        <v>12586400</v>
       </c>
       <c r="G46" s="3">
-        <v>11413400</v>
+        <v>11043800</v>
       </c>
       <c r="H46" s="3">
-        <v>10886400</v>
+        <v>11585300</v>
       </c>
       <c r="I46" s="3">
-        <v>10679900</v>
+        <v>11050400</v>
       </c>
       <c r="J46" s="3">
+        <v>10840800</v>
+      </c>
+      <c r="K46" s="3">
         <v>10378800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10570100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12713000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11858400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9223400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7681500</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1407200</v>
+        <v>1585100</v>
       </c>
       <c r="E47" s="3">
-        <v>1318400</v>
+        <v>1428400</v>
       </c>
       <c r="F47" s="3">
-        <v>1160100</v>
+        <v>1338200</v>
       </c>
       <c r="G47" s="3">
-        <v>1212900</v>
+        <v>1177500</v>
       </c>
       <c r="H47" s="3">
-        <v>1207200</v>
+        <v>1231200</v>
       </c>
       <c r="I47" s="3">
-        <v>1905400</v>
+        <v>1225400</v>
       </c>
       <c r="J47" s="3">
+        <v>1934100</v>
+      </c>
+      <c r="K47" s="3">
         <v>448900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>629500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>543000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>555400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>460200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2873400</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>8498800</v>
+        <v>4900400</v>
       </c>
       <c r="E48" s="3">
-        <v>3295500</v>
+        <v>8626800</v>
       </c>
       <c r="F48" s="3">
-        <v>2819800</v>
+        <v>3345100</v>
       </c>
       <c r="G48" s="3">
-        <v>2691500</v>
+        <v>2862300</v>
       </c>
       <c r="H48" s="3">
-        <v>2191400</v>
+        <v>2732100</v>
       </c>
       <c r="I48" s="3">
-        <v>6492100</v>
+        <v>2224400</v>
       </c>
       <c r="J48" s="3">
+        <v>6589800</v>
+      </c>
+      <c r="K48" s="3">
         <v>2086500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2026800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2617400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2716800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2322700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1996300</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3968500</v>
+        <v>2242500</v>
       </c>
       <c r="E49" s="3">
-        <v>636700</v>
+        <v>4028200</v>
       </c>
       <c r="F49" s="3">
-        <v>481700</v>
+        <v>646300</v>
       </c>
       <c r="G49" s="3">
-        <v>404900</v>
+        <v>488900</v>
       </c>
       <c r="H49" s="3">
-        <v>331700</v>
+        <v>411000</v>
       </c>
       <c r="I49" s="3">
-        <v>941400</v>
+        <v>336600</v>
       </c>
       <c r="J49" s="3">
+        <v>955500</v>
+      </c>
+      <c r="K49" s="3">
         <v>305800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>417300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>305700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>332800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>262700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>238600</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,51 +2479,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>8646700</v>
+        <v>10001600</v>
       </c>
       <c r="E52" s="3">
-        <v>7406900</v>
+        <v>8776900</v>
       </c>
       <c r="F52" s="3">
-        <v>5835600</v>
+        <v>7518400</v>
       </c>
       <c r="G52" s="3">
-        <v>5122300</v>
+        <v>5923500</v>
       </c>
       <c r="H52" s="3">
-        <v>4610400</v>
+        <v>5199500</v>
       </c>
       <c r="I52" s="3">
-        <v>9459500</v>
+        <v>4679900</v>
       </c>
       <c r="J52" s="3">
+        <v>9601900</v>
+      </c>
+      <c r="K52" s="3">
         <v>4512600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4710600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5641700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4762500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3580900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>405700</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>31640000</v>
+        <v>36121300</v>
       </c>
       <c r="E54" s="3">
-        <v>25057100</v>
+        <v>32116500</v>
       </c>
       <c r="F54" s="3">
-        <v>21177100</v>
+        <v>25434400</v>
       </c>
       <c r="G54" s="3">
-        <v>20845100</v>
+        <v>21496000</v>
       </c>
       <c r="H54" s="3">
-        <v>19227100</v>
+        <v>21159000</v>
       </c>
       <c r="I54" s="3">
-        <v>18806900</v>
+        <v>19516700</v>
       </c>
       <c r="J54" s="3">
+        <v>19090100</v>
+      </c>
+      <c r="K54" s="3">
         <v>17732700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17958400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21820800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>20225800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15850000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13195600</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,260 +2655,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>6039500</v>
+        <v>2028100</v>
       </c>
       <c r="E57" s="3">
-        <v>2605100</v>
+        <v>6130400</v>
       </c>
       <c r="F57" s="3">
-        <v>2148800</v>
+        <v>2644300</v>
       </c>
       <c r="G57" s="3">
-        <v>1950700</v>
+        <v>2181100</v>
       </c>
       <c r="H57" s="3">
-        <v>2036900</v>
+        <v>1980000</v>
       </c>
       <c r="I57" s="3">
-        <v>3799700</v>
+        <v>2067600</v>
       </c>
       <c r="J57" s="3">
+        <v>3856900</v>
+      </c>
+      <c r="K57" s="3">
         <v>1698900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1845800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2011600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2313200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2209100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1765800</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>8511000</v>
+        <v>4470600</v>
       </c>
       <c r="E58" s="3">
-        <v>3348800</v>
+        <v>8639200</v>
       </c>
       <c r="F58" s="3">
-        <v>2430500</v>
+        <v>3399200</v>
       </c>
       <c r="G58" s="3">
-        <v>2566600</v>
+        <v>2467100</v>
       </c>
       <c r="H58" s="3">
-        <v>2321700</v>
+        <v>2605300</v>
       </c>
       <c r="I58" s="3">
-        <v>7249600</v>
+        <v>2356700</v>
       </c>
       <c r="J58" s="3">
+        <v>7358800</v>
+      </c>
+      <c r="K58" s="3">
         <v>2251600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2441300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2534100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2607600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1701300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1718500</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3239700</v>
+        <v>3564600</v>
       </c>
       <c r="E59" s="3">
-        <v>2769400</v>
+        <v>3288500</v>
       </c>
       <c r="F59" s="3">
-        <v>2236200</v>
+        <v>2811100</v>
       </c>
       <c r="G59" s="3">
-        <v>2134300</v>
+        <v>2269900</v>
       </c>
       <c r="H59" s="3">
-        <v>1768900</v>
+        <v>2166400</v>
       </c>
       <c r="I59" s="3">
-        <v>3821500</v>
+        <v>1795600</v>
       </c>
       <c r="J59" s="3">
+        <v>3879000</v>
+      </c>
+      <c r="K59" s="3">
         <v>1604600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1480200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1887400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1988100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1496900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1269900</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10514900</v>
+        <v>10063200</v>
       </c>
       <c r="E60" s="3">
-        <v>8723200</v>
+        <v>10673300</v>
       </c>
       <c r="F60" s="3">
-        <v>6815500</v>
+        <v>8854600</v>
       </c>
       <c r="G60" s="3">
-        <v>6651600</v>
+        <v>6918100</v>
       </c>
       <c r="H60" s="3">
-        <v>6127500</v>
+        <v>6751700</v>
       </c>
       <c r="I60" s="3">
-        <v>6091900</v>
+        <v>6219800</v>
       </c>
       <c r="J60" s="3">
+        <v>6183600</v>
+      </c>
+      <c r="K60" s="3">
         <v>5555100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5728000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6433100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6908900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5407200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4754200</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6442200</v>
+        <v>8943400</v>
       </c>
       <c r="E61" s="3">
-        <v>3918800</v>
+        <v>6539300</v>
       </c>
       <c r="F61" s="3">
-        <v>3375800</v>
+        <v>3977800</v>
       </c>
       <c r="G61" s="3">
-        <v>3429200</v>
+        <v>3426600</v>
       </c>
       <c r="H61" s="3">
-        <v>3264000</v>
+        <v>3480800</v>
       </c>
       <c r="I61" s="3">
-        <v>3136900</v>
+        <v>3313100</v>
       </c>
       <c r="J61" s="3">
+        <v>3184100</v>
+      </c>
+      <c r="K61" s="3">
         <v>3179900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3008800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4228400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3032900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2484800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1635600</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>722300</v>
+        <v>830400</v>
       </c>
       <c r="E62" s="3">
-        <v>562000</v>
+        <v>733100</v>
       </c>
       <c r="F62" s="3">
-        <v>533200</v>
+        <v>570400</v>
       </c>
       <c r="G62" s="3">
-        <v>557200</v>
+        <v>541300</v>
       </c>
       <c r="H62" s="3">
-        <v>364100</v>
+        <v>565600</v>
       </c>
       <c r="I62" s="3">
-        <v>979700</v>
+        <v>369600</v>
       </c>
       <c r="J62" s="3">
+        <v>994400</v>
+      </c>
+      <c r="K62" s="3">
         <v>552100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>582100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>768900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>668100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>589500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>532800</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>19193300</v>
+        <v>21456600</v>
       </c>
       <c r="E66" s="3">
-        <v>13914900</v>
+        <v>19482400</v>
       </c>
       <c r="F66" s="3">
-        <v>11376200</v>
+        <v>14124500</v>
       </c>
       <c r="G66" s="3">
-        <v>11264600</v>
+        <v>11547500</v>
       </c>
       <c r="H66" s="3">
-        <v>10330500</v>
+        <v>11434300</v>
       </c>
       <c r="I66" s="3">
-        <v>10234000</v>
+        <v>10486100</v>
       </c>
       <c r="J66" s="3">
+        <v>10388200</v>
+      </c>
+      <c r="K66" s="3">
         <v>9772900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9873600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12121000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11242200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8955100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7401000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>10154200</v>
+        <v>11415400</v>
       </c>
       <c r="E72" s="3">
-        <v>9559100</v>
+        <v>10307100</v>
       </c>
       <c r="F72" s="3">
-        <v>8803100</v>
+        <v>9703100</v>
       </c>
       <c r="G72" s="3">
-        <v>8225800</v>
+        <v>8935600</v>
       </c>
       <c r="H72" s="3">
-        <v>7539000</v>
+        <v>8349700</v>
       </c>
       <c r="I72" s="3">
-        <v>13983700</v>
+        <v>7652600</v>
       </c>
       <c r="J72" s="3">
+        <v>14194300</v>
+      </c>
+      <c r="K72" s="3">
         <v>6513500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6305200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7207300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6950700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5587500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5146800</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>12446600</v>
+        <v>14664700</v>
       </c>
       <c r="E76" s="3">
-        <v>11142200</v>
+        <v>12634100</v>
       </c>
       <c r="F76" s="3">
-        <v>9800900</v>
+        <v>11310000</v>
       </c>
       <c r="G76" s="3">
-        <v>9580400</v>
+        <v>9948500</v>
       </c>
       <c r="H76" s="3">
-        <v>8896600</v>
+        <v>9724700</v>
       </c>
       <c r="I76" s="3">
-        <v>8572900</v>
+        <v>9030600</v>
       </c>
       <c r="J76" s="3">
+        <v>8702000</v>
+      </c>
+      <c r="K76" s="3">
         <v>7959800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8084800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9699800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8983500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6894900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5794600</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42094</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41729</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41364</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40999</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1037000</v>
+        <v>1607200</v>
       </c>
       <c r="E81" s="3">
-        <v>1180600</v>
+        <v>1054600</v>
       </c>
       <c r="F81" s="3">
-        <v>853400</v>
+        <v>1198400</v>
       </c>
       <c r="G81" s="3">
-        <v>989700</v>
+        <v>866200</v>
       </c>
       <c r="H81" s="3">
-        <v>920300</v>
+        <v>1004700</v>
       </c>
       <c r="I81" s="3">
-        <v>847400</v>
+        <v>934100</v>
       </c>
       <c r="J81" s="3">
+        <v>860200</v>
+      </c>
+      <c r="K81" s="3">
         <v>879700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>780700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1233500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1265300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>669800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>546000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>565800</v>
+        <v>723000</v>
       </c>
       <c r="E83" s="3">
-        <v>476100</v>
+        <v>574300</v>
       </c>
       <c r="F83" s="3">
-        <v>447100</v>
+        <v>483300</v>
       </c>
       <c r="G83" s="3">
-        <v>413300</v>
+        <v>453800</v>
       </c>
       <c r="H83" s="3">
-        <v>329500</v>
+        <v>419500</v>
       </c>
       <c r="I83" s="3">
-        <v>299700</v>
+        <v>334500</v>
       </c>
       <c r="J83" s="3">
+        <v>304200</v>
+      </c>
+      <c r="K83" s="3">
         <v>288000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>221200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>336900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>339700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>265900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>212100</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-51000</v>
+        <v>-116400</v>
       </c>
       <c r="E89" s="3">
-        <v>614300</v>
+        <v>-51800</v>
       </c>
       <c r="F89" s="3">
-        <v>949000</v>
+        <v>623500</v>
       </c>
       <c r="G89" s="3">
-        <v>547200</v>
+        <v>963300</v>
       </c>
       <c r="H89" s="3">
-        <v>591900</v>
+        <v>555400</v>
       </c>
       <c r="I89" s="3">
-        <v>910900</v>
+        <v>600900</v>
       </c>
       <c r="J89" s="3">
+        <v>924600</v>
+      </c>
+      <c r="K89" s="3">
         <v>1228300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1397000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>740000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>800700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>463400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>708700</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-893500</v>
+        <v>-1162500</v>
       </c>
       <c r="E91" s="3">
-        <v>-647000</v>
+        <v>-907000</v>
       </c>
       <c r="F91" s="3">
-        <v>-404500</v>
+        <v>-656700</v>
       </c>
       <c r="G91" s="3">
-        <v>-506300</v>
+        <v>-410600</v>
       </c>
       <c r="H91" s="3">
-        <v>-420900</v>
+        <v>-513900</v>
       </c>
       <c r="I91" s="3">
-        <v>-815900</v>
+        <v>-427300</v>
       </c>
       <c r="J91" s="3">
+        <v>-828100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-372800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-278400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-411300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-510800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-424000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-239200</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2114800</v>
+        <v>-1169000</v>
       </c>
       <c r="E94" s="3">
-        <v>-845700</v>
+        <v>-2146700</v>
       </c>
       <c r="F94" s="3">
-        <v>-313000</v>
+        <v>-858500</v>
       </c>
       <c r="G94" s="3">
-        <v>-607400</v>
+        <v>-317700</v>
       </c>
       <c r="H94" s="3">
-        <v>-390100</v>
+        <v>-616500</v>
       </c>
       <c r="I94" s="3">
-        <v>-305300</v>
+        <v>-396000</v>
       </c>
       <c r="J94" s="3">
+        <v>-309900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1112400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-923900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1035200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1001400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-629400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-620300</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,50 +4221,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-341700</v>
+        <v>-367200</v>
       </c>
       <c r="E96" s="3">
-        <v>-320900</v>
+        <v>-346900</v>
       </c>
       <c r="F96" s="3">
-        <v>-291200</v>
+        <v>-325800</v>
       </c>
       <c r="G96" s="3">
-        <v>-286000</v>
+        <v>-295600</v>
       </c>
       <c r="H96" s="3">
-        <v>-270200</v>
+        <v>-290300</v>
       </c>
       <c r="I96" s="3">
-        <v>-255100</v>
+        <v>-274300</v>
       </c>
       <c r="J96" s="3">
+        <v>-259000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-231300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-264900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-330400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-229400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-182700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-157000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,133 +4398,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1876200</v>
+        <v>1202400</v>
       </c>
       <c r="E100" s="3">
-        <v>402300</v>
+        <v>1904400</v>
       </c>
       <c r="F100" s="3">
-        <v>-453900</v>
+        <v>408300</v>
       </c>
       <c r="G100" s="3">
-        <v>-142900</v>
+        <v>-460700</v>
       </c>
       <c r="H100" s="3">
-        <v>-184700</v>
+        <v>-145000</v>
       </c>
       <c r="I100" s="3">
-        <v>-216300</v>
+        <v>-187500</v>
       </c>
       <c r="J100" s="3">
+        <v>-219600</v>
+      </c>
+      <c r="K100" s="3">
         <v>75500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-196200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>463400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>30900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>196800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-117700</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>71600</v>
+        <v>58200</v>
       </c>
       <c r="E101" s="3">
-        <v>66400</v>
+        <v>72700</v>
       </c>
       <c r="F101" s="3">
-        <v>-27700</v>
+        <v>67400</v>
       </c>
       <c r="G101" s="3">
-        <v>7400</v>
+        <v>-28200</v>
       </c>
       <c r="H101" s="3">
-        <v>-27700</v>
+        <v>7500</v>
       </c>
       <c r="I101" s="3">
-        <v>17800</v>
+        <v>-28100</v>
       </c>
       <c r="J101" s="3">
+        <v>18000</v>
+      </c>
+      <c r="K101" s="3">
         <v>-37800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-36900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>60800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>47100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>59800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-12700</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-218100</v>
+        <v>-24800</v>
       </c>
       <c r="E102" s="3">
-        <v>237200</v>
+        <v>-221300</v>
       </c>
       <c r="F102" s="3">
-        <v>154400</v>
+        <v>240800</v>
       </c>
       <c r="G102" s="3">
-        <v>-195600</v>
+        <v>156700</v>
       </c>
       <c r="H102" s="3">
-        <v>-10600</v>
+        <v>-198500</v>
       </c>
       <c r="I102" s="3">
-        <v>407100</v>
+        <v>-10800</v>
       </c>
       <c r="J102" s="3">
+        <v>413200</v>
+      </c>
+      <c r="K102" s="3">
         <v>153600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>240100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>229000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-122700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>90700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-42000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/KUBTY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KUBTY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>KUBTY</t>
   </si>
@@ -727,25 +727,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>20359600</v>
+        <v>19272100</v>
       </c>
       <c r="E8" s="3">
-        <v>18042800</v>
+        <v>17079100</v>
       </c>
       <c r="F8" s="3">
-        <v>14806200</v>
+        <v>14015400</v>
       </c>
       <c r="G8" s="3">
-        <v>12490800</v>
+        <v>11823600</v>
       </c>
       <c r="H8" s="3">
-        <v>12941100</v>
+        <v>12249900</v>
       </c>
       <c r="I8" s="3">
-        <v>12471100</v>
+        <v>11805000</v>
       </c>
       <c r="J8" s="3">
-        <v>11802000</v>
+        <v>11171600</v>
       </c>
       <c r="K8" s="3">
         <v>10598000</v>
@@ -772,25 +772,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>14452200</v>
+        <v>13680300</v>
       </c>
       <c r="E9" s="3">
-        <v>13421400</v>
+        <v>12704500</v>
       </c>
       <c r="F9" s="3">
-        <v>10547800</v>
+        <v>9984400</v>
       </c>
       <c r="G9" s="3">
-        <v>8885900</v>
+        <v>8411300</v>
       </c>
       <c r="H9" s="3">
-        <v>9167200</v>
+        <v>8677500</v>
       </c>
       <c r="I9" s="3">
-        <v>8916500</v>
+        <v>8440300</v>
       </c>
       <c r="J9" s="3">
-        <v>16710200</v>
+        <v>15817700</v>
       </c>
       <c r="K9" s="3">
         <v>7453700</v>
@@ -817,25 +817,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>5907400</v>
+        <v>5591900</v>
       </c>
       <c r="E10" s="3">
-        <v>4621500</v>
+        <v>4374600</v>
       </c>
       <c r="F10" s="3">
-        <v>4258400</v>
+        <v>4030900</v>
       </c>
       <c r="G10" s="3">
-        <v>3604900</v>
+        <v>3412300</v>
       </c>
       <c r="H10" s="3">
-        <v>3773900</v>
+        <v>3572300</v>
       </c>
       <c r="I10" s="3">
-        <v>3554600</v>
+        <v>3364700</v>
       </c>
       <c r="J10" s="3">
-        <v>-4908200</v>
+        <v>-4646100</v>
       </c>
       <c r="K10" s="3">
         <v>3144300</v>
@@ -970,26 +970,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-4400</v>
       </c>
       <c r="E14" s="3">
-        <v>13100</v>
+        <v>12400</v>
       </c>
       <c r="F14" s="3">
-        <v>3900</v>
+        <v>3700</v>
       </c>
       <c r="G14" s="3">
-        <v>-9500</v>
+        <v>-9000</v>
       </c>
       <c r="H14" s="3">
-        <v>-8900</v>
+        <v>-8400</v>
       </c>
       <c r="I14" s="3">
-        <v>-13500</v>
+        <v>-12700</v>
       </c>
       <c r="J14" s="3">
-        <v>6000</v>
+        <v>5700</v>
       </c>
       <c r="K14" s="3">
         <v>1300</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>18143300</v>
+        <v>17174200</v>
       </c>
       <c r="E17" s="3">
-        <v>16597900</v>
+        <v>15711300</v>
       </c>
       <c r="F17" s="3">
-        <v>13157800</v>
+        <v>12455000</v>
       </c>
       <c r="G17" s="3">
-        <v>11309400</v>
+        <v>10705300</v>
       </c>
       <c r="H17" s="3">
-        <v>11581900</v>
+        <v>10963300</v>
       </c>
       <c r="I17" s="3">
-        <v>11195200</v>
+        <v>10597200</v>
       </c>
       <c r="J17" s="3">
-        <v>10454300</v>
+        <v>9895900</v>
       </c>
       <c r="K17" s="3">
         <v>9344600</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2216300</v>
+        <v>2097900</v>
       </c>
       <c r="E18" s="3">
-        <v>1445000</v>
+        <v>1367800</v>
       </c>
       <c r="F18" s="3">
-        <v>1648400</v>
+        <v>1560300</v>
       </c>
       <c r="G18" s="3">
-        <v>1181400</v>
+        <v>1118300</v>
       </c>
       <c r="H18" s="3">
-        <v>1359100</v>
+        <v>1286600</v>
       </c>
       <c r="I18" s="3">
-        <v>1276000</v>
+        <v>1207800</v>
       </c>
       <c r="J18" s="3">
-        <v>1347700</v>
+        <v>1275700</v>
       </c>
       <c r="K18" s="3">
         <v>1253500</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>90700</v>
+        <v>114000</v>
       </c>
       <c r="E20" s="3">
-        <v>123800</v>
+        <v>117200</v>
       </c>
       <c r="F20" s="3">
-        <v>49500</v>
+        <v>46900</v>
       </c>
       <c r="G20" s="3">
-        <v>78500</v>
+        <v>74400</v>
       </c>
       <c r="H20" s="3">
-        <v>56800</v>
+        <v>53700</v>
       </c>
       <c r="I20" s="3">
-        <v>60400</v>
+        <v>57100</v>
       </c>
       <c r="J20" s="3">
-        <v>100900</v>
+        <v>95500</v>
       </c>
       <c r="K20" s="3">
         <v>57700</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3033200</v>
+        <v>2895200</v>
       </c>
       <c r="E21" s="3">
-        <v>2145600</v>
+        <v>2027800</v>
       </c>
       <c r="F21" s="3">
-        <v>2183300</v>
+        <v>2063900</v>
       </c>
       <c r="G21" s="3">
-        <v>1715800</v>
+        <v>1621600</v>
       </c>
       <c r="H21" s="3">
-        <v>1837300</v>
+        <v>1736800</v>
       </c>
       <c r="I21" s="3">
-        <v>1672300</v>
+        <v>1581100</v>
       </c>
       <c r="J21" s="3">
-        <v>1754200</v>
+        <v>1658700</v>
       </c>
       <c r="K21" s="3">
         <v>1597900</v>
@@ -1275,26 +1275,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>28100</v>
       </c>
       <c r="E22" s="3">
-        <v>10800</v>
+        <v>10200</v>
       </c>
       <c r="F22" s="3">
+        <v>6300</v>
+      </c>
+      <c r="G22" s="3">
+        <v>6600</v>
+      </c>
+      <c r="H22" s="3">
         <v>6700</v>
       </c>
-      <c r="G22" s="3">
-        <v>7000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>7100</v>
-      </c>
       <c r="I22" s="3">
-        <v>7000</v>
+        <v>6600</v>
       </c>
       <c r="J22" s="3">
-        <v>6200</v>
+        <v>5800</v>
       </c>
       <c r="K22" s="3">
         <v>3300</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2307000</v>
+        <v>2183800</v>
       </c>
       <c r="E23" s="3">
-        <v>1558000</v>
+        <v>1474700</v>
       </c>
       <c r="F23" s="3">
-        <v>1691200</v>
+        <v>1600900</v>
       </c>
       <c r="G23" s="3">
-        <v>1253000</v>
+        <v>1186000</v>
       </c>
       <c r="H23" s="3">
-        <v>1408800</v>
+        <v>1333600</v>
       </c>
       <c r="I23" s="3">
-        <v>1329300</v>
+        <v>1258300</v>
       </c>
       <c r="J23" s="3">
-        <v>1442400</v>
+        <v>1365400</v>
       </c>
       <c r="K23" s="3">
         <v>1307900</v>
@@ -1366,25 +1366,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>568900</v>
+        <v>538500</v>
       </c>
       <c r="E24" s="3">
-        <v>393300</v>
+        <v>372300</v>
       </c>
       <c r="F24" s="3">
-        <v>436500</v>
+        <v>413100</v>
       </c>
       <c r="G24" s="3">
-        <v>317000</v>
+        <v>300000</v>
       </c>
       <c r="H24" s="3">
-        <v>357200</v>
+        <v>338200</v>
       </c>
       <c r="I24" s="3">
-        <v>331100</v>
+        <v>313400</v>
       </c>
       <c r="J24" s="3">
-        <v>423000</v>
+        <v>400400</v>
       </c>
       <c r="K24" s="3">
         <v>375500</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1738200</v>
+        <v>1645300</v>
       </c>
       <c r="E26" s="3">
-        <v>1164700</v>
+        <v>1102500</v>
       </c>
       <c r="F26" s="3">
-        <v>1254700</v>
+        <v>1187700</v>
       </c>
       <c r="G26" s="3">
-        <v>936000</v>
+        <v>886000</v>
       </c>
       <c r="H26" s="3">
-        <v>1051600</v>
+        <v>995400</v>
       </c>
       <c r="I26" s="3">
-        <v>998300</v>
+        <v>944900</v>
       </c>
       <c r="J26" s="3">
-        <v>1019400</v>
+        <v>964900</v>
       </c>
       <c r="K26" s="3">
         <v>932400</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1607200</v>
+        <v>1521300</v>
       </c>
       <c r="E27" s="3">
-        <v>1054600</v>
+        <v>998300</v>
       </c>
       <c r="F27" s="3">
-        <v>1198400</v>
+        <v>1115000</v>
       </c>
       <c r="G27" s="3">
-        <v>866200</v>
+        <v>820000</v>
       </c>
       <c r="H27" s="3">
-        <v>1004700</v>
+        <v>951000</v>
       </c>
       <c r="I27" s="3">
-        <v>934100</v>
+        <v>884200</v>
       </c>
       <c r="J27" s="3">
-        <v>930400</v>
+        <v>880700</v>
       </c>
       <c r="K27" s="3">
         <v>879700</v>
@@ -1609,7 +1609,7 @@
         <v>8</v>
       </c>
       <c r="J29" s="3">
-        <v>-70200</v>
+        <v>-66500</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-90700</v>
+        <v>-114000</v>
       </c>
       <c r="E32" s="3">
-        <v>-123800</v>
+        <v>-117200</v>
       </c>
       <c r="F32" s="3">
-        <v>-49500</v>
+        <v>-46900</v>
       </c>
       <c r="G32" s="3">
-        <v>-78500</v>
+        <v>-74400</v>
       </c>
       <c r="H32" s="3">
-        <v>-56800</v>
+        <v>-53700</v>
       </c>
       <c r="I32" s="3">
-        <v>-60400</v>
+        <v>-57100</v>
       </c>
       <c r="J32" s="3">
-        <v>-100900</v>
+        <v>-95500</v>
       </c>
       <c r="K32" s="3">
         <v>-57700</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1607200</v>
+        <v>1521300</v>
       </c>
       <c r="E33" s="3">
-        <v>1054600</v>
+        <v>998300</v>
       </c>
       <c r="F33" s="3">
-        <v>1198400</v>
+        <v>1115000</v>
       </c>
       <c r="G33" s="3">
-        <v>866200</v>
+        <v>820000</v>
       </c>
       <c r="H33" s="3">
-        <v>1004700</v>
+        <v>951000</v>
       </c>
       <c r="I33" s="3">
-        <v>934100</v>
+        <v>884200</v>
       </c>
       <c r="J33" s="3">
-        <v>860200</v>
+        <v>814300</v>
       </c>
       <c r="K33" s="3">
         <v>879700</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1607200</v>
+        <v>1521300</v>
       </c>
       <c r="E35" s="3">
-        <v>1054600</v>
+        <v>998300</v>
       </c>
       <c r="F35" s="3">
-        <v>1198400</v>
+        <v>1115000</v>
       </c>
       <c r="G35" s="3">
-        <v>866200</v>
+        <v>820000</v>
       </c>
       <c r="H35" s="3">
-        <v>1004700</v>
+        <v>951000</v>
       </c>
       <c r="I35" s="3">
-        <v>934100</v>
+        <v>884200</v>
       </c>
       <c r="J35" s="3">
-        <v>860200</v>
+        <v>814300</v>
       </c>
       <c r="K35" s="3">
         <v>879700</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1497100</v>
+        <v>1073200</v>
       </c>
       <c r="E41" s="3">
-        <v>2744700</v>
+        <v>2598100</v>
       </c>
       <c r="F41" s="3">
-        <v>3143000</v>
+        <v>2975100</v>
       </c>
       <c r="G41" s="3">
-        <v>1502500</v>
+        <v>1422200</v>
       </c>
       <c r="H41" s="3">
-        <v>1345700</v>
+        <v>1273900</v>
       </c>
       <c r="I41" s="3">
-        <v>1544300</v>
+        <v>1461800</v>
       </c>
       <c r="J41" s="3">
-        <v>3110100</v>
+        <v>2944000</v>
       </c>
       <c r="K41" s="3">
         <v>1124900</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>559500</v>
+        <v>873500</v>
       </c>
       <c r="E42" s="3">
-        <v>781100</v>
+        <v>739400</v>
       </c>
       <c r="F42" s="3">
-        <v>686400</v>
+        <v>649700</v>
       </c>
       <c r="G42" s="3">
-        <v>336800</v>
+        <v>318800</v>
       </c>
       <c r="H42" s="3">
-        <v>485100</v>
+        <v>459200</v>
       </c>
       <c r="I42" s="3">
-        <v>366500</v>
+        <v>346900</v>
       </c>
       <c r="J42" s="3">
-        <v>359100</v>
+        <v>339900</v>
       </c>
       <c r="K42" s="3">
         <v>40500</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>10456000</v>
+        <v>9897600</v>
       </c>
       <c r="E43" s="3">
-        <v>13952900</v>
+        <v>13207600</v>
       </c>
       <c r="F43" s="3">
-        <v>6664000</v>
+        <v>6308000</v>
       </c>
       <c r="G43" s="3">
-        <v>6196400</v>
+        <v>5865500</v>
       </c>
       <c r="H43" s="3">
-        <v>6624200</v>
+        <v>6270400</v>
       </c>
       <c r="I43" s="3">
-        <v>6282200</v>
+        <v>5946700</v>
       </c>
       <c r="J43" s="3">
-        <v>16597600</v>
+        <v>15711100</v>
       </c>
       <c r="K43" s="3">
         <v>5823300</v>
@@ -2129,25 +2129,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4502600</v>
+        <v>4262100</v>
       </c>
       <c r="E44" s="3">
-        <v>8687500</v>
+        <v>8223400</v>
       </c>
       <c r="F44" s="3">
-        <v>3437800</v>
+        <v>3254200</v>
       </c>
       <c r="G44" s="3">
-        <v>2520700</v>
+        <v>2386100</v>
       </c>
       <c r="H44" s="3">
-        <v>2577400</v>
+        <v>2439700</v>
       </c>
       <c r="I44" s="3">
-        <v>2498500</v>
+        <v>2365100</v>
       </c>
       <c r="J44" s="3">
-        <v>4862000</v>
+        <v>4602400</v>
       </c>
       <c r="K44" s="3">
         <v>2365000</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>376400</v>
+        <v>356300</v>
       </c>
       <c r="E45" s="3">
-        <v>372200</v>
+        <v>352300</v>
       </c>
       <c r="F45" s="3">
-        <v>398400</v>
+        <v>377200</v>
       </c>
       <c r="G45" s="3">
-        <v>487300</v>
+        <v>461300</v>
       </c>
       <c r="H45" s="3">
-        <v>552900</v>
+        <v>523400</v>
       </c>
       <c r="I45" s="3">
-        <v>358900</v>
+        <v>339700</v>
       </c>
       <c r="J45" s="3">
-        <v>1108000</v>
+        <v>1048800</v>
       </c>
       <c r="K45" s="3">
         <v>1025100</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>17391700</v>
+        <v>16462800</v>
       </c>
       <c r="E46" s="3">
-        <v>15419600</v>
+        <v>14596000</v>
       </c>
       <c r="F46" s="3">
-        <v>12586400</v>
+        <v>11914100</v>
       </c>
       <c r="G46" s="3">
-        <v>11043800</v>
+        <v>10453900</v>
       </c>
       <c r="H46" s="3">
-        <v>11585300</v>
+        <v>10966500</v>
       </c>
       <c r="I46" s="3">
-        <v>11050400</v>
+        <v>10460200</v>
       </c>
       <c r="J46" s="3">
-        <v>10840800</v>
+        <v>10261800</v>
       </c>
       <c r="K46" s="3">
         <v>10378800</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1585100</v>
+        <v>10107300</v>
       </c>
       <c r="E47" s="3">
-        <v>1428400</v>
+        <v>9032700</v>
       </c>
       <c r="F47" s="3">
-        <v>1338200</v>
+        <v>7833400</v>
       </c>
       <c r="G47" s="3">
-        <v>1177500</v>
+        <v>6265500</v>
       </c>
       <c r="H47" s="3">
-        <v>1231200</v>
+        <v>5626500</v>
       </c>
       <c r="I47" s="3">
-        <v>1225400</v>
+        <v>5127600</v>
       </c>
       <c r="J47" s="3">
-        <v>1934100</v>
+        <v>5400300</v>
       </c>
       <c r="K47" s="3">
         <v>448900</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4900400</v>
+        <v>4638600</v>
       </c>
       <c r="E48" s="3">
-        <v>8626800</v>
+        <v>8220600</v>
       </c>
       <c r="F48" s="3">
-        <v>3345100</v>
+        <v>3166500</v>
       </c>
       <c r="G48" s="3">
-        <v>2862300</v>
+        <v>2709400</v>
       </c>
       <c r="H48" s="3">
-        <v>2732100</v>
+        <v>2586100</v>
       </c>
       <c r="I48" s="3">
-        <v>2224400</v>
+        <v>2105600</v>
       </c>
       <c r="J48" s="3">
-        <v>6589800</v>
+        <v>6237800</v>
       </c>
       <c r="K48" s="3">
         <v>2086500</v>
@@ -2354,25 +2354,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2242500</v>
+        <v>2122700</v>
       </c>
       <c r="E49" s="3">
-        <v>4028200</v>
+        <v>4069000</v>
       </c>
       <c r="F49" s="3">
-        <v>646300</v>
+        <v>611700</v>
       </c>
       <c r="G49" s="3">
-        <v>488900</v>
+        <v>462800</v>
       </c>
       <c r="H49" s="3">
-        <v>411000</v>
+        <v>389100</v>
       </c>
       <c r="I49" s="3">
-        <v>336600</v>
+        <v>318700</v>
       </c>
       <c r="J49" s="3">
-        <v>955500</v>
+        <v>904500</v>
       </c>
       <c r="K49" s="3">
         <v>305800</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10001600</v>
+        <v>860500</v>
       </c>
       <c r="E52" s="3">
-        <v>8776900</v>
+        <v>627500</v>
       </c>
       <c r="F52" s="3">
-        <v>7518400</v>
+        <v>550200</v>
       </c>
       <c r="G52" s="3">
-        <v>5923500</v>
+        <v>456300</v>
       </c>
       <c r="H52" s="3">
-        <v>5199500</v>
+        <v>460600</v>
       </c>
       <c r="I52" s="3">
-        <v>4679900</v>
+        <v>462300</v>
       </c>
       <c r="J52" s="3">
-        <v>9601900</v>
+        <v>5519600</v>
       </c>
       <c r="K52" s="3">
         <v>4512600</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>36121300</v>
+        <v>34192000</v>
       </c>
       <c r="E54" s="3">
-        <v>32116500</v>
+        <v>30401000</v>
       </c>
       <c r="F54" s="3">
-        <v>25434400</v>
+        <v>24075900</v>
       </c>
       <c r="G54" s="3">
-        <v>21496000</v>
+        <v>20347800</v>
       </c>
       <c r="H54" s="3">
-        <v>21159000</v>
+        <v>20028800</v>
       </c>
       <c r="I54" s="3">
-        <v>19516700</v>
+        <v>18474300</v>
       </c>
       <c r="J54" s="3">
-        <v>19090100</v>
+        <v>18070500</v>
       </c>
       <c r="K54" s="3">
         <v>17732700</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2028100</v>
+        <v>1919800</v>
       </c>
       <c r="E57" s="3">
-        <v>6130400</v>
+        <v>5803000</v>
       </c>
       <c r="F57" s="3">
-        <v>2644300</v>
+        <v>2503100</v>
       </c>
       <c r="G57" s="3">
-        <v>2181100</v>
+        <v>2064600</v>
       </c>
       <c r="H57" s="3">
-        <v>1980000</v>
+        <v>1874300</v>
       </c>
       <c r="I57" s="3">
-        <v>2067600</v>
+        <v>1957100</v>
       </c>
       <c r="J57" s="3">
-        <v>3856900</v>
+        <v>3650900</v>
       </c>
       <c r="K57" s="3">
         <v>1698900</v>
@@ -2707,25 +2707,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4470600</v>
+        <v>4231800</v>
       </c>
       <c r="E58" s="3">
-        <v>8639200</v>
+        <v>8177700</v>
       </c>
       <c r="F58" s="3">
-        <v>3399200</v>
+        <v>3217700</v>
       </c>
       <c r="G58" s="3">
-        <v>2467100</v>
+        <v>2335300</v>
       </c>
       <c r="H58" s="3">
-        <v>2605300</v>
+        <v>2466100</v>
       </c>
       <c r="I58" s="3">
-        <v>2356700</v>
+        <v>2230800</v>
       </c>
       <c r="J58" s="3">
-        <v>7358800</v>
+        <v>6965700</v>
       </c>
       <c r="K58" s="3">
         <v>2251600</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3564600</v>
+        <v>3374200</v>
       </c>
       <c r="E59" s="3">
-        <v>3288500</v>
+        <v>3112800</v>
       </c>
       <c r="F59" s="3">
-        <v>2811100</v>
+        <v>2660900</v>
       </c>
       <c r="G59" s="3">
-        <v>2269900</v>
+        <v>2148700</v>
       </c>
       <c r="H59" s="3">
-        <v>2166400</v>
+        <v>2050700</v>
       </c>
       <c r="I59" s="3">
-        <v>1795600</v>
+        <v>1699700</v>
       </c>
       <c r="J59" s="3">
-        <v>3879000</v>
+        <v>3671900</v>
       </c>
       <c r="K59" s="3">
         <v>1604600</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10063200</v>
+        <v>9525700</v>
       </c>
       <c r="E60" s="3">
-        <v>10673300</v>
+        <v>10103200</v>
       </c>
       <c r="F60" s="3">
-        <v>8854600</v>
+        <v>8381700</v>
       </c>
       <c r="G60" s="3">
-        <v>6918100</v>
+        <v>6548600</v>
       </c>
       <c r="H60" s="3">
-        <v>6751700</v>
+        <v>6391100</v>
       </c>
       <c r="I60" s="3">
-        <v>6219800</v>
+        <v>5887600</v>
       </c>
       <c r="J60" s="3">
-        <v>6183600</v>
+        <v>5853400</v>
       </c>
       <c r="K60" s="3">
         <v>5555100</v>
@@ -2842,25 +2842,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8943400</v>
+        <v>8465700</v>
       </c>
       <c r="E61" s="3">
-        <v>6539300</v>
+        <v>6190000</v>
       </c>
       <c r="F61" s="3">
-        <v>3977800</v>
+        <v>3765300</v>
       </c>
       <c r="G61" s="3">
-        <v>3426600</v>
+        <v>3243600</v>
       </c>
       <c r="H61" s="3">
-        <v>3480800</v>
+        <v>3294900</v>
       </c>
       <c r="I61" s="3">
-        <v>3313100</v>
+        <v>3136200</v>
       </c>
       <c r="J61" s="3">
-        <v>3184100</v>
+        <v>3014100</v>
       </c>
       <c r="K61" s="3">
         <v>3179900</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>830400</v>
+        <v>786000</v>
       </c>
       <c r="E62" s="3">
-        <v>733100</v>
+        <v>694000</v>
       </c>
       <c r="F62" s="3">
-        <v>570400</v>
+        <v>540000</v>
       </c>
       <c r="G62" s="3">
-        <v>541300</v>
+        <v>512400</v>
       </c>
       <c r="H62" s="3">
-        <v>565600</v>
+        <v>535400</v>
       </c>
       <c r="I62" s="3">
-        <v>369600</v>
+        <v>349900</v>
       </c>
       <c r="J62" s="3">
-        <v>994400</v>
+        <v>941300</v>
       </c>
       <c r="K62" s="3">
         <v>552100</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>21456600</v>
+        <v>20310600</v>
       </c>
       <c r="E66" s="3">
-        <v>19482400</v>
+        <v>18441800</v>
       </c>
       <c r="F66" s="3">
-        <v>14124500</v>
+        <v>13370100</v>
       </c>
       <c r="G66" s="3">
-        <v>11547500</v>
+        <v>10930700</v>
       </c>
       <c r="H66" s="3">
-        <v>11434300</v>
+        <v>10823500</v>
       </c>
       <c r="I66" s="3">
-        <v>10486100</v>
+        <v>9926000</v>
       </c>
       <c r="J66" s="3">
-        <v>10388200</v>
+        <v>9833300</v>
       </c>
       <c r="K66" s="3">
         <v>9772900</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>11415400</v>
+        <v>10805700</v>
       </c>
       <c r="E72" s="3">
-        <v>10307100</v>
+        <v>9756600</v>
       </c>
       <c r="F72" s="3">
-        <v>9703100</v>
+        <v>9184800</v>
       </c>
       <c r="G72" s="3">
-        <v>8935600</v>
+        <v>8458400</v>
       </c>
       <c r="H72" s="3">
-        <v>8349700</v>
+        <v>7903700</v>
       </c>
       <c r="I72" s="3">
-        <v>7652600</v>
+        <v>7243800</v>
       </c>
       <c r="J72" s="3">
-        <v>14194300</v>
+        <v>13436200</v>
       </c>
       <c r="K72" s="3">
         <v>6513500</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>14664700</v>
+        <v>13881400</v>
       </c>
       <c r="E76" s="3">
-        <v>12634100</v>
+        <v>11959200</v>
       </c>
       <c r="F76" s="3">
-        <v>11310000</v>
+        <v>10705900</v>
       </c>
       <c r="G76" s="3">
-        <v>9948500</v>
+        <v>9417100</v>
       </c>
       <c r="H76" s="3">
-        <v>9724700</v>
+        <v>9205300</v>
       </c>
       <c r="I76" s="3">
-        <v>9030600</v>
+        <v>8548200</v>
       </c>
       <c r="J76" s="3">
-        <v>8702000</v>
+        <v>8237200</v>
       </c>
       <c r="K76" s="3">
         <v>7959800</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1607200</v>
+        <v>1521300</v>
       </c>
       <c r="E81" s="3">
-        <v>1054600</v>
+        <v>998300</v>
       </c>
       <c r="F81" s="3">
-        <v>1198400</v>
+        <v>1115000</v>
       </c>
       <c r="G81" s="3">
-        <v>866200</v>
+        <v>820000</v>
       </c>
       <c r="H81" s="3">
-        <v>1004700</v>
+        <v>951000</v>
       </c>
       <c r="I81" s="3">
-        <v>934100</v>
+        <v>884200</v>
       </c>
       <c r="J81" s="3">
-        <v>860200</v>
+        <v>814300</v>
       </c>
       <c r="K81" s="3">
         <v>879700</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>723000</v>
+        <v>684400</v>
       </c>
       <c r="E83" s="3">
-        <v>574300</v>
+        <v>543700</v>
       </c>
       <c r="F83" s="3">
-        <v>483300</v>
+        <v>457500</v>
       </c>
       <c r="G83" s="3">
-        <v>453800</v>
+        <v>429600</v>
       </c>
       <c r="H83" s="3">
-        <v>419500</v>
+        <v>397100</v>
       </c>
       <c r="I83" s="3">
-        <v>334500</v>
+        <v>316600</v>
       </c>
       <c r="J83" s="3">
-        <v>304200</v>
+        <v>288000</v>
       </c>
       <c r="K83" s="3">
         <v>288000</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-116400</v>
+        <v>-110200</v>
       </c>
       <c r="E89" s="3">
-        <v>-51800</v>
+        <v>-49000</v>
       </c>
       <c r="F89" s="3">
-        <v>623500</v>
+        <v>590200</v>
       </c>
       <c r="G89" s="3">
-        <v>963300</v>
+        <v>911800</v>
       </c>
       <c r="H89" s="3">
-        <v>555400</v>
+        <v>525800</v>
       </c>
       <c r="I89" s="3">
-        <v>600900</v>
+        <v>568800</v>
       </c>
       <c r="J89" s="3">
-        <v>924600</v>
+        <v>875200</v>
       </c>
       <c r="K89" s="3">
         <v>1228300</v>
@@ -4029,25 +4029,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1162500</v>
+        <v>-956200</v>
       </c>
       <c r="E91" s="3">
-        <v>-907000</v>
+        <v>-858600</v>
       </c>
       <c r="F91" s="3">
-        <v>-656700</v>
+        <v>-621600</v>
       </c>
       <c r="G91" s="3">
-        <v>-410600</v>
+        <v>-388600</v>
       </c>
       <c r="H91" s="3">
-        <v>-513900</v>
+        <v>-486400</v>
       </c>
       <c r="I91" s="3">
-        <v>-427300</v>
+        <v>-404500</v>
       </c>
       <c r="J91" s="3">
-        <v>-828100</v>
+        <v>-783900</v>
       </c>
       <c r="K91" s="3">
         <v>-372800</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1169000</v>
+        <v>-1106600</v>
       </c>
       <c r="E94" s="3">
-        <v>-2146700</v>
+        <v>-2032000</v>
       </c>
       <c r="F94" s="3">
-        <v>-858500</v>
+        <v>-812600</v>
       </c>
       <c r="G94" s="3">
-        <v>-317700</v>
+        <v>-300700</v>
       </c>
       <c r="H94" s="3">
-        <v>-616500</v>
+        <v>-583600</v>
       </c>
       <c r="I94" s="3">
-        <v>-396000</v>
+        <v>-374900</v>
       </c>
       <c r="J94" s="3">
-        <v>-309900</v>
+        <v>-293400</v>
       </c>
       <c r="K94" s="3">
         <v>-1112400</v>
@@ -4228,25 +4228,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-367200</v>
+        <v>-347600</v>
       </c>
       <c r="E96" s="3">
-        <v>-346900</v>
+        <v>-328400</v>
       </c>
       <c r="F96" s="3">
-        <v>-325800</v>
+        <v>-308400</v>
       </c>
       <c r="G96" s="3">
-        <v>-295600</v>
+        <v>-279800</v>
       </c>
       <c r="H96" s="3">
-        <v>-290300</v>
+        <v>-274800</v>
       </c>
       <c r="I96" s="3">
-        <v>-274300</v>
+        <v>-259600</v>
       </c>
       <c r="J96" s="3">
-        <v>-259000</v>
+        <v>-245100</v>
       </c>
       <c r="K96" s="3">
         <v>-231300</v>
@@ -4408,25 +4408,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1202400</v>
+        <v>1138200</v>
       </c>
       <c r="E100" s="3">
-        <v>1904400</v>
+        <v>1802700</v>
       </c>
       <c r="F100" s="3">
-        <v>408300</v>
+        <v>386500</v>
       </c>
       <c r="G100" s="3">
-        <v>-460700</v>
+        <v>-436100</v>
       </c>
       <c r="H100" s="3">
-        <v>-145000</v>
+        <v>-137300</v>
       </c>
       <c r="I100" s="3">
-        <v>-187500</v>
+        <v>-177500</v>
       </c>
       <c r="J100" s="3">
-        <v>-219600</v>
+        <v>-207800</v>
       </c>
       <c r="K100" s="3">
         <v>75500</v>
@@ -4453,25 +4453,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>58200</v>
+        <v>55100</v>
       </c>
       <c r="E101" s="3">
-        <v>72700</v>
+        <v>68800</v>
       </c>
       <c r="F101" s="3">
-        <v>67400</v>
+        <v>63800</v>
       </c>
       <c r="G101" s="3">
-        <v>-28200</v>
+        <v>-26700</v>
       </c>
       <c r="H101" s="3">
-        <v>7500</v>
+        <v>7100</v>
       </c>
       <c r="I101" s="3">
-        <v>-28100</v>
+        <v>-26600</v>
       </c>
       <c r="J101" s="3">
-        <v>18000</v>
+        <v>17100</v>
       </c>
       <c r="K101" s="3">
         <v>-37800</v>
@@ -4498,25 +4498,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-24800</v>
+        <v>-23500</v>
       </c>
       <c r="E102" s="3">
-        <v>-221300</v>
+        <v>-209500</v>
       </c>
       <c r="F102" s="3">
-        <v>240800</v>
+        <v>227900</v>
       </c>
       <c r="G102" s="3">
-        <v>156700</v>
+        <v>148400</v>
       </c>
       <c r="H102" s="3">
-        <v>-198500</v>
+        <v>-187900</v>
       </c>
       <c r="I102" s="3">
-        <v>-10800</v>
+        <v>-10200</v>
       </c>
       <c r="J102" s="3">
-        <v>413200</v>
+        <v>391100</v>
       </c>
       <c r="K102" s="3">
         <v>153600</v>

--- a/AAII_Financials/Yearly/KUBTY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KUBTY_YR_FIN.xlsx
@@ -727,25 +727,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>19272100</v>
+        <v>21447000</v>
       </c>
       <c r="E8" s="3">
-        <v>17079100</v>
+        <v>19006600</v>
       </c>
       <c r="F8" s="3">
-        <v>14015400</v>
+        <v>15597000</v>
       </c>
       <c r="G8" s="3">
-        <v>11823600</v>
+        <v>13158000</v>
       </c>
       <c r="H8" s="3">
-        <v>12249900</v>
+        <v>13632300</v>
       </c>
       <c r="I8" s="3">
-        <v>11805000</v>
+        <v>13137200</v>
       </c>
       <c r="J8" s="3">
-        <v>11171600</v>
+        <v>12432400</v>
       </c>
       <c r="K8" s="3">
         <v>10598000</v>
@@ -772,25 +772,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>13680300</v>
+        <v>15224100</v>
       </c>
       <c r="E9" s="3">
-        <v>12704500</v>
+        <v>14138200</v>
       </c>
       <c r="F9" s="3">
-        <v>9984400</v>
+        <v>11111200</v>
       </c>
       <c r="G9" s="3">
-        <v>8411300</v>
+        <v>9360500</v>
       </c>
       <c r="H9" s="3">
-        <v>8677500</v>
+        <v>9656800</v>
       </c>
       <c r="I9" s="3">
-        <v>8440300</v>
+        <v>9392800</v>
       </c>
       <c r="J9" s="3">
-        <v>15817700</v>
+        <v>17602700</v>
       </c>
       <c r="K9" s="3">
         <v>7453700</v>
@@ -817,25 +817,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>5591900</v>
+        <v>6222900</v>
       </c>
       <c r="E10" s="3">
-        <v>4374600</v>
+        <v>4868300</v>
       </c>
       <c r="F10" s="3">
-        <v>4030900</v>
+        <v>4485800</v>
       </c>
       <c r="G10" s="3">
-        <v>3412300</v>
+        <v>3797400</v>
       </c>
       <c r="H10" s="3">
-        <v>3572300</v>
+        <v>3975500</v>
       </c>
       <c r="I10" s="3">
-        <v>3364700</v>
+        <v>3744400</v>
       </c>
       <c r="J10" s="3">
-        <v>-4646100</v>
+        <v>-5170400</v>
       </c>
       <c r="K10" s="3">
         <v>3144300</v>
@@ -971,25 +971,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-4400</v>
+        <v>-4900</v>
       </c>
       <c r="E14" s="3">
-        <v>12400</v>
+        <v>13800</v>
       </c>
       <c r="F14" s="3">
-        <v>3700</v>
+        <v>4100</v>
       </c>
       <c r="G14" s="3">
-        <v>-9000</v>
+        <v>-10000</v>
       </c>
       <c r="H14" s="3">
-        <v>-8400</v>
+        <v>-9400</v>
       </c>
       <c r="I14" s="3">
-        <v>-12700</v>
+        <v>-14200</v>
       </c>
       <c r="J14" s="3">
-        <v>5700</v>
+        <v>6300</v>
       </c>
       <c r="K14" s="3">
         <v>1300</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>17174200</v>
+        <v>19112400</v>
       </c>
       <c r="E17" s="3">
-        <v>15711300</v>
+        <v>17484400</v>
       </c>
       <c r="F17" s="3">
-        <v>12455000</v>
+        <v>13860600</v>
       </c>
       <c r="G17" s="3">
-        <v>10705300</v>
+        <v>11913400</v>
       </c>
       <c r="H17" s="3">
-        <v>10963300</v>
+        <v>12200600</v>
       </c>
       <c r="I17" s="3">
-        <v>10597200</v>
+        <v>11793100</v>
       </c>
       <c r="J17" s="3">
-        <v>9895900</v>
+        <v>11012700</v>
       </c>
       <c r="K17" s="3">
         <v>9344600</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2097900</v>
+        <v>2334700</v>
       </c>
       <c r="E18" s="3">
-        <v>1367800</v>
+        <v>1522100</v>
       </c>
       <c r="F18" s="3">
-        <v>1560300</v>
+        <v>1736400</v>
       </c>
       <c r="G18" s="3">
-        <v>1118300</v>
+        <v>1244500</v>
       </c>
       <c r="H18" s="3">
-        <v>1286600</v>
+        <v>1431700</v>
       </c>
       <c r="I18" s="3">
-        <v>1207800</v>
+        <v>1344100</v>
       </c>
       <c r="J18" s="3">
-        <v>1275700</v>
+        <v>1419700</v>
       </c>
       <c r="K18" s="3">
         <v>1253500</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>114000</v>
+        <v>126800</v>
       </c>
       <c r="E20" s="3">
-        <v>117200</v>
+        <v>130400</v>
       </c>
       <c r="F20" s="3">
-        <v>46900</v>
+        <v>52100</v>
       </c>
       <c r="G20" s="3">
-        <v>74400</v>
+        <v>82700</v>
       </c>
       <c r="H20" s="3">
-        <v>53700</v>
+        <v>59800</v>
       </c>
       <c r="I20" s="3">
-        <v>57100</v>
+        <v>63600</v>
       </c>
       <c r="J20" s="3">
-        <v>95500</v>
+        <v>106300</v>
       </c>
       <c r="K20" s="3">
         <v>57700</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2895200</v>
+        <v>3217800</v>
       </c>
       <c r="E21" s="3">
-        <v>2027800</v>
+        <v>2253300</v>
       </c>
       <c r="F21" s="3">
-        <v>2063900</v>
+        <v>2294000</v>
       </c>
       <c r="G21" s="3">
-        <v>1621600</v>
+        <v>1802000</v>
       </c>
       <c r="H21" s="3">
-        <v>1736800</v>
+        <v>1930400</v>
       </c>
       <c r="I21" s="3">
-        <v>1581100</v>
+        <v>1757600</v>
       </c>
       <c r="J21" s="3">
-        <v>1658700</v>
+        <v>1844200</v>
       </c>
       <c r="K21" s="3">
         <v>1597900</v>
@@ -1276,25 +1276,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>28100</v>
+        <v>31300</v>
       </c>
       <c r="E22" s="3">
-        <v>10200</v>
+        <v>11400</v>
       </c>
       <c r="F22" s="3">
-        <v>6300</v>
+        <v>7000</v>
       </c>
       <c r="G22" s="3">
-        <v>6600</v>
+        <v>7400</v>
       </c>
       <c r="H22" s="3">
-        <v>6700</v>
+        <v>7500</v>
       </c>
       <c r="I22" s="3">
-        <v>6600</v>
+        <v>7400</v>
       </c>
       <c r="J22" s="3">
-        <v>5800</v>
+        <v>6500</v>
       </c>
       <c r="K22" s="3">
         <v>3300</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2183800</v>
+        <v>2430300</v>
       </c>
       <c r="E23" s="3">
-        <v>1474700</v>
+        <v>1641200</v>
       </c>
       <c r="F23" s="3">
-        <v>1600900</v>
+        <v>1781500</v>
       </c>
       <c r="G23" s="3">
-        <v>1186000</v>
+        <v>1319900</v>
       </c>
       <c r="H23" s="3">
-        <v>1333600</v>
+        <v>1484100</v>
       </c>
       <c r="I23" s="3">
-        <v>1258300</v>
+        <v>1400300</v>
       </c>
       <c r="J23" s="3">
-        <v>1365400</v>
+        <v>1519400</v>
       </c>
       <c r="K23" s="3">
         <v>1307900</v>
@@ -1366,25 +1366,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>538500</v>
+        <v>599300</v>
       </c>
       <c r="E24" s="3">
-        <v>372300</v>
+        <v>414300</v>
       </c>
       <c r="F24" s="3">
-        <v>413100</v>
+        <v>459800</v>
       </c>
       <c r="G24" s="3">
-        <v>300000</v>
+        <v>333900</v>
       </c>
       <c r="H24" s="3">
-        <v>338200</v>
+        <v>376300</v>
       </c>
       <c r="I24" s="3">
-        <v>313400</v>
+        <v>348700</v>
       </c>
       <c r="J24" s="3">
-        <v>400400</v>
+        <v>445600</v>
       </c>
       <c r="K24" s="3">
         <v>375500</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1645300</v>
+        <v>1831000</v>
       </c>
       <c r="E26" s="3">
-        <v>1102500</v>
+        <v>1226900</v>
       </c>
       <c r="F26" s="3">
-        <v>1187700</v>
+        <v>1321700</v>
       </c>
       <c r="G26" s="3">
-        <v>886000</v>
+        <v>986000</v>
       </c>
       <c r="H26" s="3">
-        <v>995400</v>
+        <v>1107700</v>
       </c>
       <c r="I26" s="3">
-        <v>944900</v>
+        <v>1051600</v>
       </c>
       <c r="J26" s="3">
-        <v>964900</v>
+        <v>1073800</v>
       </c>
       <c r="K26" s="3">
         <v>932400</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1521300</v>
+        <v>1693000</v>
       </c>
       <c r="E27" s="3">
-        <v>998300</v>
+        <v>1111000</v>
       </c>
       <c r="F27" s="3">
-        <v>1115000</v>
+        <v>1240800</v>
       </c>
       <c r="G27" s="3">
-        <v>820000</v>
+        <v>912500</v>
       </c>
       <c r="H27" s="3">
-        <v>951000</v>
+        <v>1058300</v>
       </c>
       <c r="I27" s="3">
-        <v>884200</v>
+        <v>984000</v>
       </c>
       <c r="J27" s="3">
-        <v>880700</v>
+        <v>980100</v>
       </c>
       <c r="K27" s="3">
         <v>879700</v>
@@ -1609,7 +1609,7 @@
         <v>8</v>
       </c>
       <c r="J29" s="3">
-        <v>-66500</v>
+        <v>-74000</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-114000</v>
+        <v>-126800</v>
       </c>
       <c r="E32" s="3">
-        <v>-117200</v>
+        <v>-130400</v>
       </c>
       <c r="F32" s="3">
-        <v>-46900</v>
+        <v>-52100</v>
       </c>
       <c r="G32" s="3">
-        <v>-74400</v>
+        <v>-82700</v>
       </c>
       <c r="H32" s="3">
-        <v>-53700</v>
+        <v>-59800</v>
       </c>
       <c r="I32" s="3">
-        <v>-57100</v>
+        <v>-63600</v>
       </c>
       <c r="J32" s="3">
-        <v>-95500</v>
+        <v>-106300</v>
       </c>
       <c r="K32" s="3">
         <v>-57700</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1521300</v>
+        <v>1693000</v>
       </c>
       <c r="E33" s="3">
-        <v>998300</v>
+        <v>1111000</v>
       </c>
       <c r="F33" s="3">
-        <v>1115000</v>
+        <v>1240800</v>
       </c>
       <c r="G33" s="3">
-        <v>820000</v>
+        <v>912500</v>
       </c>
       <c r="H33" s="3">
-        <v>951000</v>
+        <v>1058300</v>
       </c>
       <c r="I33" s="3">
-        <v>884200</v>
+        <v>984000</v>
       </c>
       <c r="J33" s="3">
-        <v>814300</v>
+        <v>906100</v>
       </c>
       <c r="K33" s="3">
         <v>879700</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1521300</v>
+        <v>1693000</v>
       </c>
       <c r="E35" s="3">
-        <v>998300</v>
+        <v>1111000</v>
       </c>
       <c r="F35" s="3">
-        <v>1115000</v>
+        <v>1240800</v>
       </c>
       <c r="G35" s="3">
-        <v>820000</v>
+        <v>912500</v>
       </c>
       <c r="H35" s="3">
-        <v>951000</v>
+        <v>1058300</v>
       </c>
       <c r="I35" s="3">
-        <v>884200</v>
+        <v>984000</v>
       </c>
       <c r="J35" s="3">
-        <v>814300</v>
+        <v>906100</v>
       </c>
       <c r="K35" s="3">
         <v>879700</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1073200</v>
+        <v>1194400</v>
       </c>
       <c r="E41" s="3">
-        <v>2598100</v>
+        <v>2891300</v>
       </c>
       <c r="F41" s="3">
-        <v>2975100</v>
+        <v>3310900</v>
       </c>
       <c r="G41" s="3">
-        <v>1422200</v>
+        <v>1582700</v>
       </c>
       <c r="H41" s="3">
-        <v>1273900</v>
+        <v>1417600</v>
       </c>
       <c r="I41" s="3">
-        <v>1461800</v>
+        <v>1626800</v>
       </c>
       <c r="J41" s="3">
-        <v>2944000</v>
+        <v>3276200</v>
       </c>
       <c r="K41" s="3">
         <v>1124900</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>873500</v>
+        <v>972100</v>
       </c>
       <c r="E42" s="3">
-        <v>739400</v>
+        <v>822800</v>
       </c>
       <c r="F42" s="3">
-        <v>649700</v>
+        <v>723000</v>
       </c>
       <c r="G42" s="3">
-        <v>318800</v>
+        <v>354800</v>
       </c>
       <c r="H42" s="3">
-        <v>459200</v>
+        <v>511000</v>
       </c>
       <c r="I42" s="3">
-        <v>346900</v>
+        <v>386000</v>
       </c>
       <c r="J42" s="3">
-        <v>339900</v>
+        <v>378300</v>
       </c>
       <c r="K42" s="3">
         <v>40500</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>9897600</v>
+        <v>11014500</v>
       </c>
       <c r="E43" s="3">
-        <v>13207600</v>
+        <v>14698100</v>
       </c>
       <c r="F43" s="3">
-        <v>6308000</v>
+        <v>7019900</v>
       </c>
       <c r="G43" s="3">
-        <v>5865500</v>
+        <v>6527400</v>
       </c>
       <c r="H43" s="3">
-        <v>6270400</v>
+        <v>6978000</v>
       </c>
       <c r="I43" s="3">
-        <v>5946700</v>
+        <v>6617800</v>
       </c>
       <c r="J43" s="3">
-        <v>15711100</v>
+        <v>17484100</v>
       </c>
       <c r="K43" s="3">
         <v>5823300</v>
@@ -2129,25 +2129,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4262100</v>
+        <v>4743100</v>
       </c>
       <c r="E44" s="3">
-        <v>8223400</v>
+        <v>9151500</v>
       </c>
       <c r="F44" s="3">
-        <v>3254200</v>
+        <v>3621500</v>
       </c>
       <c r="G44" s="3">
-        <v>2386100</v>
+        <v>2655400</v>
       </c>
       <c r="H44" s="3">
-        <v>2439700</v>
+        <v>2715000</v>
       </c>
       <c r="I44" s="3">
-        <v>2365100</v>
+        <v>2632000</v>
       </c>
       <c r="J44" s="3">
-        <v>4602400</v>
+        <v>5121700</v>
       </c>
       <c r="K44" s="3">
         <v>2365000</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>356300</v>
+        <v>396500</v>
       </c>
       <c r="E45" s="3">
-        <v>352300</v>
+        <v>392100</v>
       </c>
       <c r="F45" s="3">
-        <v>377200</v>
+        <v>419700</v>
       </c>
       <c r="G45" s="3">
-        <v>461300</v>
+        <v>513400</v>
       </c>
       <c r="H45" s="3">
-        <v>523400</v>
+        <v>582400</v>
       </c>
       <c r="I45" s="3">
-        <v>339700</v>
+        <v>378100</v>
       </c>
       <c r="J45" s="3">
-        <v>1048800</v>
+        <v>1167200</v>
       </c>
       <c r="K45" s="3">
         <v>1025100</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>16462800</v>
+        <v>18320600</v>
       </c>
       <c r="E46" s="3">
-        <v>14596000</v>
+        <v>16243200</v>
       </c>
       <c r="F46" s="3">
-        <v>11914100</v>
+        <v>13258600</v>
       </c>
       <c r="G46" s="3">
-        <v>10453900</v>
+        <v>11633600</v>
       </c>
       <c r="H46" s="3">
-        <v>10966500</v>
+        <v>12204100</v>
       </c>
       <c r="I46" s="3">
-        <v>10460200</v>
+        <v>11640600</v>
       </c>
       <c r="J46" s="3">
-        <v>10261800</v>
+        <v>11419800</v>
       </c>
       <c r="K46" s="3">
         <v>10378800</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>10107300</v>
+        <v>11248000</v>
       </c>
       <c r="E47" s="3">
-        <v>9032700</v>
+        <v>10052100</v>
       </c>
       <c r="F47" s="3">
-        <v>7833400</v>
+        <v>8717500</v>
       </c>
       <c r="G47" s="3">
-        <v>6265500</v>
+        <v>6972500</v>
       </c>
       <c r="H47" s="3">
-        <v>5626500</v>
+        <v>6261500</v>
       </c>
       <c r="I47" s="3">
-        <v>5127600</v>
+        <v>5706200</v>
       </c>
       <c r="J47" s="3">
-        <v>5400300</v>
+        <v>6009700</v>
       </c>
       <c r="K47" s="3">
         <v>448900</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4638600</v>
+        <v>5162100</v>
       </c>
       <c r="E48" s="3">
-        <v>8220600</v>
+        <v>9148300</v>
       </c>
       <c r="F48" s="3">
-        <v>3166500</v>
+        <v>3523800</v>
       </c>
       <c r="G48" s="3">
-        <v>2709400</v>
+        <v>3015200</v>
       </c>
       <c r="H48" s="3">
-        <v>2586100</v>
+        <v>2878000</v>
       </c>
       <c r="I48" s="3">
-        <v>2105600</v>
+        <v>2343200</v>
       </c>
       <c r="J48" s="3">
-        <v>6237800</v>
+        <v>6941800</v>
       </c>
       <c r="K48" s="3">
         <v>2086500</v>
@@ -2354,25 +2354,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2122700</v>
+        <v>2362300</v>
       </c>
       <c r="E49" s="3">
-        <v>4069000</v>
+        <v>4528200</v>
       </c>
       <c r="F49" s="3">
-        <v>611700</v>
+        <v>680800</v>
       </c>
       <c r="G49" s="3">
-        <v>462800</v>
+        <v>515000</v>
       </c>
       <c r="H49" s="3">
-        <v>389100</v>
+        <v>433000</v>
       </c>
       <c r="I49" s="3">
-        <v>318700</v>
+        <v>354600</v>
       </c>
       <c r="J49" s="3">
-        <v>904500</v>
+        <v>1006600</v>
       </c>
       <c r="K49" s="3">
         <v>305800</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>860500</v>
+        <v>957600</v>
       </c>
       <c r="E52" s="3">
-        <v>627500</v>
+        <v>698300</v>
       </c>
       <c r="F52" s="3">
-        <v>550200</v>
+        <v>612200</v>
       </c>
       <c r="G52" s="3">
-        <v>456300</v>
+        <v>507800</v>
       </c>
       <c r="H52" s="3">
-        <v>460600</v>
+        <v>512600</v>
       </c>
       <c r="I52" s="3">
-        <v>462300</v>
+        <v>514400</v>
       </c>
       <c r="J52" s="3">
-        <v>5519600</v>
+        <v>6142500</v>
       </c>
       <c r="K52" s="3">
         <v>4512600</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>34192000</v>
+        <v>38050700</v>
       </c>
       <c r="E54" s="3">
-        <v>30401000</v>
+        <v>33831900</v>
       </c>
       <c r="F54" s="3">
-        <v>24075900</v>
+        <v>26793000</v>
       </c>
       <c r="G54" s="3">
-        <v>20347800</v>
+        <v>22644200</v>
       </c>
       <c r="H54" s="3">
-        <v>20028800</v>
+        <v>22289200</v>
       </c>
       <c r="I54" s="3">
-        <v>18474300</v>
+        <v>20559200</v>
       </c>
       <c r="J54" s="3">
-        <v>18070500</v>
+        <v>20109800</v>
       </c>
       <c r="K54" s="3">
         <v>17732700</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1919800</v>
+        <v>2136400</v>
       </c>
       <c r="E57" s="3">
-        <v>5803000</v>
+        <v>6457900</v>
       </c>
       <c r="F57" s="3">
-        <v>2503100</v>
+        <v>2785600</v>
       </c>
       <c r="G57" s="3">
-        <v>2064600</v>
+        <v>2297600</v>
       </c>
       <c r="H57" s="3">
-        <v>1874300</v>
+        <v>2085800</v>
       </c>
       <c r="I57" s="3">
-        <v>1957100</v>
+        <v>2178000</v>
       </c>
       <c r="J57" s="3">
-        <v>3650900</v>
+        <v>4062900</v>
       </c>
       <c r="K57" s="3">
         <v>1698900</v>
@@ -2707,25 +2707,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4231800</v>
+        <v>4709400</v>
       </c>
       <c r="E58" s="3">
-        <v>8177700</v>
+        <v>9100600</v>
       </c>
       <c r="F58" s="3">
-        <v>3217700</v>
+        <v>3580800</v>
       </c>
       <c r="G58" s="3">
-        <v>2335300</v>
+        <v>2598900</v>
       </c>
       <c r="H58" s="3">
-        <v>2466100</v>
+        <v>2744400</v>
       </c>
       <c r="I58" s="3">
-        <v>2230800</v>
+        <v>2482600</v>
       </c>
       <c r="J58" s="3">
-        <v>6965700</v>
+        <v>7751800</v>
       </c>
       <c r="K58" s="3">
         <v>2251600</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3374200</v>
+        <v>3754900</v>
       </c>
       <c r="E59" s="3">
-        <v>3112800</v>
+        <v>3464100</v>
       </c>
       <c r="F59" s="3">
-        <v>2660900</v>
+        <v>2961200</v>
       </c>
       <c r="G59" s="3">
-        <v>2148700</v>
+        <v>2391100</v>
       </c>
       <c r="H59" s="3">
-        <v>2050700</v>
+        <v>2282200</v>
       </c>
       <c r="I59" s="3">
-        <v>1699700</v>
+        <v>1891500</v>
       </c>
       <c r="J59" s="3">
-        <v>3671900</v>
+        <v>4086200</v>
       </c>
       <c r="K59" s="3">
         <v>1604600</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>9525700</v>
+        <v>10600700</v>
       </c>
       <c r="E60" s="3">
-        <v>10103200</v>
+        <v>11243400</v>
       </c>
       <c r="F60" s="3">
-        <v>8381700</v>
+        <v>9327500</v>
       </c>
       <c r="G60" s="3">
-        <v>6548600</v>
+        <v>7287600</v>
       </c>
       <c r="H60" s="3">
-        <v>6391100</v>
+        <v>7112400</v>
       </c>
       <c r="I60" s="3">
-        <v>5887600</v>
+        <v>6552000</v>
       </c>
       <c r="J60" s="3">
-        <v>5853400</v>
+        <v>6513900</v>
       </c>
       <c r="K60" s="3">
         <v>5555100</v>
@@ -2842,25 +2842,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8465700</v>
+        <v>9421100</v>
       </c>
       <c r="E61" s="3">
-        <v>6190000</v>
+        <v>6888500</v>
       </c>
       <c r="F61" s="3">
-        <v>3765300</v>
+        <v>4190200</v>
       </c>
       <c r="G61" s="3">
-        <v>3243600</v>
+        <v>3609600</v>
       </c>
       <c r="H61" s="3">
-        <v>3294900</v>
+        <v>3666700</v>
       </c>
       <c r="I61" s="3">
-        <v>3136200</v>
+        <v>3490100</v>
       </c>
       <c r="J61" s="3">
-        <v>3014100</v>
+        <v>3354200</v>
       </c>
       <c r="K61" s="3">
         <v>3179900</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>786000</v>
+        <v>874800</v>
       </c>
       <c r="E62" s="3">
-        <v>694000</v>
+        <v>772300</v>
       </c>
       <c r="F62" s="3">
-        <v>540000</v>
+        <v>600900</v>
       </c>
       <c r="G62" s="3">
-        <v>512400</v>
+        <v>570200</v>
       </c>
       <c r="H62" s="3">
-        <v>535400</v>
+        <v>595800</v>
       </c>
       <c r="I62" s="3">
-        <v>349900</v>
+        <v>389300</v>
       </c>
       <c r="J62" s="3">
-        <v>941300</v>
+        <v>1047600</v>
       </c>
       <c r="K62" s="3">
         <v>552100</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>20310600</v>
+        <v>22602700</v>
       </c>
       <c r="E66" s="3">
-        <v>18441800</v>
+        <v>20523000</v>
       </c>
       <c r="F66" s="3">
-        <v>13370100</v>
+        <v>14878900</v>
       </c>
       <c r="G66" s="3">
-        <v>10930700</v>
+        <v>12164300</v>
       </c>
       <c r="H66" s="3">
-        <v>10823500</v>
+        <v>12045000</v>
       </c>
       <c r="I66" s="3">
-        <v>9926000</v>
+        <v>11046200</v>
       </c>
       <c r="J66" s="3">
-        <v>9833300</v>
+        <v>10943000</v>
       </c>
       <c r="K66" s="3">
         <v>9772900</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>10805700</v>
+        <v>12025100</v>
       </c>
       <c r="E72" s="3">
-        <v>9756600</v>
+        <v>10857700</v>
       </c>
       <c r="F72" s="3">
-        <v>9184800</v>
+        <v>10221400</v>
       </c>
       <c r="G72" s="3">
-        <v>8458400</v>
+        <v>9412900</v>
       </c>
       <c r="H72" s="3">
-        <v>7903700</v>
+        <v>8795700</v>
       </c>
       <c r="I72" s="3">
-        <v>7243800</v>
+        <v>8061300</v>
       </c>
       <c r="J72" s="3">
-        <v>13436200</v>
+        <v>14952500</v>
       </c>
       <c r="K72" s="3">
         <v>6513500</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>13881400</v>
+        <v>15448000</v>
       </c>
       <c r="E76" s="3">
-        <v>11959200</v>
+        <v>13308900</v>
       </c>
       <c r="F76" s="3">
-        <v>10705900</v>
+        <v>11914000</v>
       </c>
       <c r="G76" s="3">
-        <v>9417100</v>
+        <v>10479900</v>
       </c>
       <c r="H76" s="3">
-        <v>9205300</v>
+        <v>10244100</v>
       </c>
       <c r="I76" s="3">
-        <v>8548200</v>
+        <v>9512900</v>
       </c>
       <c r="J76" s="3">
-        <v>8237200</v>
+        <v>9166800</v>
       </c>
       <c r="K76" s="3">
         <v>7959800</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1521300</v>
+        <v>1693000</v>
       </c>
       <c r="E81" s="3">
-        <v>998300</v>
+        <v>1111000</v>
       </c>
       <c r="F81" s="3">
-        <v>1115000</v>
+        <v>1240800</v>
       </c>
       <c r="G81" s="3">
-        <v>820000</v>
+        <v>912500</v>
       </c>
       <c r="H81" s="3">
-        <v>951000</v>
+        <v>1058300</v>
       </c>
       <c r="I81" s="3">
-        <v>884200</v>
+        <v>984000</v>
       </c>
       <c r="J81" s="3">
-        <v>814300</v>
+        <v>906100</v>
       </c>
       <c r="K81" s="3">
         <v>879700</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>684400</v>
+        <v>761600</v>
       </c>
       <c r="E83" s="3">
-        <v>543700</v>
+        <v>605000</v>
       </c>
       <c r="F83" s="3">
-        <v>457500</v>
+        <v>509100</v>
       </c>
       <c r="G83" s="3">
-        <v>429600</v>
+        <v>478100</v>
       </c>
       <c r="H83" s="3">
-        <v>397100</v>
+        <v>441900</v>
       </c>
       <c r="I83" s="3">
-        <v>316600</v>
+        <v>352300</v>
       </c>
       <c r="J83" s="3">
-        <v>288000</v>
+        <v>320500</v>
       </c>
       <c r="K83" s="3">
         <v>288000</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-110200</v>
+        <v>-122600</v>
       </c>
       <c r="E89" s="3">
-        <v>-49000</v>
+        <v>-54500</v>
       </c>
       <c r="F89" s="3">
-        <v>590200</v>
+        <v>656800</v>
       </c>
       <c r="G89" s="3">
-        <v>911800</v>
+        <v>1014700</v>
       </c>
       <c r="H89" s="3">
-        <v>525800</v>
+        <v>585100</v>
       </c>
       <c r="I89" s="3">
-        <v>568800</v>
+        <v>633000</v>
       </c>
       <c r="J89" s="3">
-        <v>875200</v>
+        <v>974000</v>
       </c>
       <c r="K89" s="3">
         <v>1228300</v>
@@ -4029,25 +4029,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-956200</v>
+        <v>-1064200</v>
       </c>
       <c r="E91" s="3">
-        <v>-858600</v>
+        <v>-955400</v>
       </c>
       <c r="F91" s="3">
-        <v>-621600</v>
+        <v>-691800</v>
       </c>
       <c r="G91" s="3">
-        <v>-388600</v>
+        <v>-432500</v>
       </c>
       <c r="H91" s="3">
-        <v>-486400</v>
+        <v>-541300</v>
       </c>
       <c r="I91" s="3">
-        <v>-404500</v>
+        <v>-450100</v>
       </c>
       <c r="J91" s="3">
-        <v>-783900</v>
+        <v>-872400</v>
       </c>
       <c r="K91" s="3">
         <v>-372800</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1106600</v>
+        <v>-1231400</v>
       </c>
       <c r="E94" s="3">
-        <v>-2032000</v>
+        <v>-2261300</v>
       </c>
       <c r="F94" s="3">
-        <v>-812600</v>
+        <v>-904300</v>
       </c>
       <c r="G94" s="3">
-        <v>-300700</v>
+        <v>-334600</v>
       </c>
       <c r="H94" s="3">
-        <v>-583600</v>
+        <v>-649400</v>
       </c>
       <c r="I94" s="3">
-        <v>-374900</v>
+        <v>-417200</v>
       </c>
       <c r="J94" s="3">
-        <v>-293400</v>
+        <v>-326500</v>
       </c>
       <c r="K94" s="3">
         <v>-1112400</v>
@@ -4228,25 +4228,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-347600</v>
+        <v>-386800</v>
       </c>
       <c r="E96" s="3">
-        <v>-328400</v>
+        <v>-365400</v>
       </c>
       <c r="F96" s="3">
-        <v>-308400</v>
+        <v>-343200</v>
       </c>
       <c r="G96" s="3">
-        <v>-279800</v>
+        <v>-311400</v>
       </c>
       <c r="H96" s="3">
-        <v>-274800</v>
+        <v>-305800</v>
       </c>
       <c r="I96" s="3">
-        <v>-259600</v>
+        <v>-288900</v>
       </c>
       <c r="J96" s="3">
-        <v>-245100</v>
+        <v>-272800</v>
       </c>
       <c r="K96" s="3">
         <v>-231300</v>
@@ -4408,25 +4408,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1138200</v>
+        <v>1266700</v>
       </c>
       <c r="E100" s="3">
-        <v>1802700</v>
+        <v>2006200</v>
       </c>
       <c r="F100" s="3">
-        <v>386500</v>
+        <v>430200</v>
       </c>
       <c r="G100" s="3">
-        <v>-436100</v>
+        <v>-485300</v>
       </c>
       <c r="H100" s="3">
-        <v>-137300</v>
+        <v>-152800</v>
       </c>
       <c r="I100" s="3">
-        <v>-177500</v>
+        <v>-197500</v>
       </c>
       <c r="J100" s="3">
-        <v>-207800</v>
+        <v>-231300</v>
       </c>
       <c r="K100" s="3">
         <v>75500</v>
@@ -4453,25 +4453,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>55100</v>
+        <v>61300</v>
       </c>
       <c r="E101" s="3">
-        <v>68800</v>
+        <v>76600</v>
       </c>
       <c r="F101" s="3">
-        <v>63800</v>
+        <v>71000</v>
       </c>
       <c r="G101" s="3">
-        <v>-26700</v>
+        <v>-29700</v>
       </c>
       <c r="H101" s="3">
-        <v>7100</v>
+        <v>7900</v>
       </c>
       <c r="I101" s="3">
-        <v>-26600</v>
+        <v>-29600</v>
       </c>
       <c r="J101" s="3">
-        <v>17100</v>
+        <v>19000</v>
       </c>
       <c r="K101" s="3">
         <v>-37800</v>
@@ -4498,25 +4498,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-23500</v>
+        <v>-26100</v>
       </c>
       <c r="E102" s="3">
-        <v>-209500</v>
+        <v>-233200</v>
       </c>
       <c r="F102" s="3">
-        <v>227900</v>
+        <v>253600</v>
       </c>
       <c r="G102" s="3">
-        <v>148400</v>
+        <v>165100</v>
       </c>
       <c r="H102" s="3">
-        <v>-187900</v>
+        <v>-209200</v>
       </c>
       <c r="I102" s="3">
-        <v>-10200</v>
+        <v>-11300</v>
       </c>
       <c r="J102" s="3">
-        <v>391100</v>
+        <v>435300</v>
       </c>
       <c r="K102" s="3">
         <v>153600</v>

--- a/AAII_Financials/Yearly/KUBTY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KUBTY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>KUBTY</t>
   </si>
@@ -727,25 +727,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>21447000</v>
+        <v>21429300</v>
       </c>
       <c r="E8" s="3">
-        <v>19006600</v>
+        <v>20299700</v>
       </c>
       <c r="F8" s="3">
-        <v>15597000</v>
+        <v>19079400</v>
       </c>
       <c r="G8" s="3">
-        <v>13158000</v>
+        <v>17956500</v>
       </c>
       <c r="H8" s="3">
-        <v>13632300</v>
+        <v>17667400</v>
       </c>
       <c r="I8" s="3">
-        <v>13137200</v>
+        <v>16864700</v>
       </c>
       <c r="J8" s="3">
-        <v>12432400</v>
+        <v>15550500</v>
       </c>
       <c r="K8" s="3">
         <v>10598000</v>
@@ -772,25 +772,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>15224100</v>
+        <v>15211500</v>
       </c>
       <c r="E9" s="3">
-        <v>14138200</v>
+        <v>15100100</v>
       </c>
       <c r="F9" s="3">
-        <v>11111200</v>
+        <v>13592000</v>
       </c>
       <c r="G9" s="3">
-        <v>9360500</v>
+        <v>12774200</v>
       </c>
       <c r="H9" s="3">
-        <v>9656800</v>
+        <v>12515200</v>
       </c>
       <c r="I9" s="3">
-        <v>9392800</v>
+        <v>12057900</v>
       </c>
       <c r="J9" s="3">
-        <v>17602700</v>
+        <v>11015300</v>
       </c>
       <c r="K9" s="3">
         <v>7453700</v>
@@ -817,25 +817,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>6222900</v>
+        <v>6217800</v>
       </c>
       <c r="E10" s="3">
-        <v>4868300</v>
+        <v>5199500</v>
       </c>
       <c r="F10" s="3">
-        <v>4485800</v>
+        <v>5487400</v>
       </c>
       <c r="G10" s="3">
-        <v>3797400</v>
+        <v>5182300</v>
       </c>
       <c r="H10" s="3">
-        <v>3975500</v>
+        <v>5152200</v>
       </c>
       <c r="I10" s="3">
-        <v>3744400</v>
+        <v>4806900</v>
       </c>
       <c r="J10" s="3">
-        <v>-5170400</v>
+        <v>4535300</v>
       </c>
       <c r="K10" s="3">
         <v>3144300</v>
@@ -880,26 +880,26 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>710200</v>
+      </c>
+      <c r="E12" s="3">
+        <v>669900</v>
+      </c>
+      <c r="F12" s="3">
+        <v>567000</v>
+      </c>
+      <c r="G12" s="3">
+        <v>536200</v>
+      </c>
+      <c r="H12" s="3">
+        <v>488700</v>
+      </c>
+      <c r="I12" s="3">
+        <v>490700</v>
+      </c>
+      <c r="J12" s="3">
+        <v>427100</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -971,25 +971,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-4900</v>
+        <v>-46200</v>
       </c>
       <c r="E14" s="3">
-        <v>13800</v>
+        <v>42200</v>
       </c>
       <c r="F14" s="3">
-        <v>4100</v>
+        <v>25400</v>
       </c>
       <c r="G14" s="3">
-        <v>-10000</v>
+        <v>14600</v>
       </c>
       <c r="H14" s="3">
-        <v>-9400</v>
+        <v>40000</v>
       </c>
       <c r="I14" s="3">
-        <v>-14200</v>
+        <v>11000</v>
       </c>
       <c r="J14" s="3">
-        <v>6300</v>
+        <v>-65700</v>
       </c>
       <c r="K14" s="3">
         <v>1300</v>
@@ -1016,25 +1016,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>486000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>428100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>382200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>408700</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>366400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>397100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>402100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>19112400</v>
+        <v>19080700</v>
       </c>
       <c r="E17" s="3">
-        <v>17484400</v>
+        <v>18722900</v>
       </c>
       <c r="F17" s="3">
-        <v>13860600</v>
+        <v>16975100</v>
       </c>
       <c r="G17" s="3">
-        <v>11913400</v>
+        <v>16202200</v>
       </c>
       <c r="H17" s="3">
-        <v>12200600</v>
+        <v>15741100</v>
       </c>
       <c r="I17" s="3">
-        <v>11793100</v>
+        <v>15067400</v>
       </c>
       <c r="J17" s="3">
-        <v>11012700</v>
+        <v>13776400</v>
       </c>
       <c r="K17" s="3">
         <v>9344600</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2334700</v>
+        <v>2348600</v>
       </c>
       <c r="E18" s="3">
-        <v>1522100</v>
+        <v>1576800</v>
       </c>
       <c r="F18" s="3">
-        <v>1736400</v>
+        <v>2104400</v>
       </c>
       <c r="G18" s="3">
-        <v>1244500</v>
+        <v>1754300</v>
       </c>
       <c r="H18" s="3">
-        <v>1431700</v>
+        <v>1926300</v>
       </c>
       <c r="I18" s="3">
-        <v>1344100</v>
+        <v>1797300</v>
       </c>
       <c r="J18" s="3">
-        <v>1419700</v>
+        <v>1774100</v>
       </c>
       <c r="K18" s="3">
         <v>1253500</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>126800</v>
+        <v>30100</v>
       </c>
       <c r="E20" s="3">
-        <v>130400</v>
+        <v>-186600</v>
       </c>
       <c r="F20" s="3">
-        <v>52100</v>
+        <v>-109200</v>
       </c>
       <c r="G20" s="3">
-        <v>82700</v>
+        <v>-33600</v>
       </c>
       <c r="H20" s="3">
-        <v>59800</v>
+        <v>1300</v>
       </c>
       <c r="I20" s="3">
-        <v>63600</v>
+        <v>34600</v>
       </c>
       <c r="J20" s="3">
-        <v>106300</v>
+        <v>-91600</v>
       </c>
       <c r="K20" s="3">
         <v>57700</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3217800</v>
+        <v>2804600</v>
       </c>
       <c r="E21" s="3">
-        <v>2253300</v>
+        <v>2191400</v>
       </c>
       <c r="F21" s="3">
-        <v>2294000</v>
+        <v>2595700</v>
       </c>
       <c r="G21" s="3">
-        <v>1802000</v>
+        <v>2196600</v>
       </c>
       <c r="H21" s="3">
-        <v>1930400</v>
+        <v>2291400</v>
       </c>
       <c r="I21" s="3">
-        <v>1757600</v>
+        <v>2159900</v>
       </c>
       <c r="J21" s="3">
-        <v>1844200</v>
+        <v>2267900</v>
       </c>
       <c r="K21" s="3">
         <v>1597900</v>
@@ -1279,22 +1279,22 @@
         <v>31300</v>
       </c>
       <c r="E22" s="3">
-        <v>11400</v>
+        <v>12100</v>
       </c>
       <c r="F22" s="3">
-        <v>7000</v>
+        <v>8600</v>
       </c>
       <c r="G22" s="3">
-        <v>7400</v>
+        <v>10100</v>
       </c>
       <c r="H22" s="3">
-        <v>7500</v>
+        <v>9700</v>
       </c>
       <c r="I22" s="3">
-        <v>7400</v>
+        <v>9500</v>
       </c>
       <c r="J22" s="3">
-        <v>6500</v>
+        <v>85800</v>
       </c>
       <c r="K22" s="3">
         <v>3300</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2430300</v>
+        <v>2443200</v>
       </c>
       <c r="E23" s="3">
-        <v>1641200</v>
+        <v>1765300</v>
       </c>
       <c r="F23" s="3">
-        <v>1781500</v>
+        <v>2220000</v>
       </c>
       <c r="G23" s="3">
-        <v>1319900</v>
+        <v>1825700</v>
       </c>
       <c r="H23" s="3">
-        <v>1484100</v>
+        <v>1951600</v>
       </c>
       <c r="I23" s="3">
-        <v>1400300</v>
+        <v>1816200</v>
       </c>
       <c r="J23" s="3">
-        <v>1519400</v>
+        <v>1911200</v>
       </c>
       <c r="K23" s="3">
         <v>1307900</v>
@@ -1366,25 +1366,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>599300</v>
+        <v>598800</v>
       </c>
       <c r="E24" s="3">
-        <v>414300</v>
+        <v>442500</v>
       </c>
       <c r="F24" s="3">
-        <v>459800</v>
+        <v>563400</v>
       </c>
       <c r="G24" s="3">
-        <v>333900</v>
+        <v>455700</v>
       </c>
       <c r="H24" s="3">
-        <v>376300</v>
+        <v>487700</v>
       </c>
       <c r="I24" s="3">
-        <v>348700</v>
+        <v>447700</v>
       </c>
       <c r="J24" s="3">
-        <v>445600</v>
+        <v>620800</v>
       </c>
       <c r="K24" s="3">
         <v>375500</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1831000</v>
+        <v>1844500</v>
       </c>
       <c r="E26" s="3">
-        <v>1226900</v>
+        <v>1322800</v>
       </c>
       <c r="F26" s="3">
-        <v>1321700</v>
+        <v>1656600</v>
       </c>
       <c r="G26" s="3">
-        <v>986000</v>
+        <v>1370100</v>
       </c>
       <c r="H26" s="3">
-        <v>1107700</v>
+        <v>1463900</v>
       </c>
       <c r="I26" s="3">
-        <v>1051600</v>
+        <v>1368500</v>
       </c>
       <c r="J26" s="3">
-        <v>1073800</v>
+        <v>1290400</v>
       </c>
       <c r="K26" s="3">
         <v>932400</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1693000</v>
+        <v>1691600</v>
       </c>
       <c r="E27" s="3">
-        <v>1111000</v>
+        <v>1186500</v>
       </c>
       <c r="F27" s="3">
-        <v>1240800</v>
+        <v>1525400</v>
       </c>
       <c r="G27" s="3">
-        <v>912500</v>
+        <v>1245300</v>
       </c>
       <c r="H27" s="3">
-        <v>1058300</v>
+        <v>1371600</v>
       </c>
       <c r="I27" s="3">
-        <v>984000</v>
+        <v>1263200</v>
       </c>
       <c r="J27" s="3">
-        <v>980100</v>
+        <v>1211400</v>
       </c>
       <c r="K27" s="3">
         <v>879700</v>
@@ -1590,26 +1590,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-74000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-126800</v>
+        <v>-30100</v>
       </c>
       <c r="E32" s="3">
-        <v>-130400</v>
+        <v>186600</v>
       </c>
       <c r="F32" s="3">
-        <v>-52100</v>
+        <v>109200</v>
       </c>
       <c r="G32" s="3">
-        <v>-82700</v>
+        <v>33600</v>
       </c>
       <c r="H32" s="3">
-        <v>-59800</v>
+        <v>-1300</v>
       </c>
       <c r="I32" s="3">
-        <v>-63600</v>
+        <v>-34600</v>
       </c>
       <c r="J32" s="3">
-        <v>-106300</v>
+        <v>91600</v>
       </c>
       <c r="K32" s="3">
         <v>-57700</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1693000</v>
+        <v>1691600</v>
       </c>
       <c r="E33" s="3">
-        <v>1111000</v>
+        <v>1186500</v>
       </c>
       <c r="F33" s="3">
-        <v>1240800</v>
+        <v>1525400</v>
       </c>
       <c r="G33" s="3">
-        <v>912500</v>
+        <v>1245300</v>
       </c>
       <c r="H33" s="3">
-        <v>1058300</v>
+        <v>1371600</v>
       </c>
       <c r="I33" s="3">
-        <v>984000</v>
+        <v>1263200</v>
       </c>
       <c r="J33" s="3">
-        <v>906100</v>
+        <v>1211400</v>
       </c>
       <c r="K33" s="3">
         <v>879700</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1693000</v>
+        <v>1691600</v>
       </c>
       <c r="E35" s="3">
-        <v>1111000</v>
+        <v>1186500</v>
       </c>
       <c r="F35" s="3">
-        <v>1240800</v>
+        <v>1525400</v>
       </c>
       <c r="G35" s="3">
-        <v>912500</v>
+        <v>1245300</v>
       </c>
       <c r="H35" s="3">
-        <v>1058300</v>
+        <v>1371600</v>
       </c>
       <c r="I35" s="3">
-        <v>984000</v>
+        <v>1263200</v>
       </c>
       <c r="J35" s="3">
-        <v>906100</v>
+        <v>1211400</v>
       </c>
       <c r="K35" s="3">
         <v>879700</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1194400</v>
+        <v>1575700</v>
       </c>
       <c r="E41" s="3">
-        <v>2891300</v>
+        <v>1712200</v>
       </c>
       <c r="F41" s="3">
-        <v>3310900</v>
+        <v>2246300</v>
       </c>
       <c r="G41" s="3">
-        <v>1582700</v>
+        <v>2159900</v>
       </c>
       <c r="H41" s="3">
-        <v>1417600</v>
+        <v>1837200</v>
       </c>
       <c r="I41" s="3">
-        <v>1626800</v>
+        <v>2088300</v>
       </c>
       <c r="J41" s="3">
-        <v>3276200</v>
+        <v>2048400</v>
       </c>
       <c r="K41" s="3">
         <v>1124900</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>972100</v>
+        <v>588900</v>
       </c>
       <c r="E42" s="3">
-        <v>822800</v>
+        <v>542300</v>
       </c>
       <c r="F42" s="3">
-        <v>723000</v>
+        <v>441900</v>
       </c>
       <c r="G42" s="3">
-        <v>354800</v>
+        <v>484100</v>
       </c>
       <c r="H42" s="3">
-        <v>511000</v>
+        <v>662200</v>
       </c>
       <c r="I42" s="3">
-        <v>386000</v>
+        <v>495600</v>
       </c>
       <c r="J42" s="3">
-        <v>378300</v>
+        <v>11400</v>
       </c>
       <c r="K42" s="3">
         <v>40500</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>11014500</v>
+        <v>11005400</v>
       </c>
       <c r="E43" s="3">
-        <v>14698100</v>
+        <v>9788000</v>
       </c>
       <c r="F43" s="3">
-        <v>7019900</v>
+        <v>8369500</v>
       </c>
       <c r="G43" s="3">
-        <v>6527400</v>
+        <v>8907900</v>
       </c>
       <c r="H43" s="3">
-        <v>6978000</v>
+        <v>9043500</v>
       </c>
       <c r="I43" s="3">
-        <v>6617800</v>
+        <v>8495500</v>
       </c>
       <c r="J43" s="3">
-        <v>17484100</v>
+        <v>8120700</v>
       </c>
       <c r="K43" s="3">
         <v>5823300</v>
@@ -2129,25 +2129,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4743100</v>
+        <v>4739200</v>
       </c>
       <c r="E44" s="3">
-        <v>9151500</v>
+        <v>4887100</v>
       </c>
       <c r="F44" s="3">
-        <v>3621500</v>
+        <v>4430000</v>
       </c>
       <c r="G44" s="3">
-        <v>2655400</v>
+        <v>3623800</v>
       </c>
       <c r="H44" s="3">
-        <v>2715000</v>
+        <v>3518700</v>
       </c>
       <c r="I44" s="3">
-        <v>2632000</v>
+        <v>3378700</v>
       </c>
       <c r="J44" s="3">
-        <v>5121700</v>
+        <v>3218500</v>
       </c>
       <c r="K44" s="3">
         <v>2365000</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>396500</v>
+        <v>396200</v>
       </c>
       <c r="E45" s="3">
-        <v>392100</v>
+        <v>418800</v>
       </c>
       <c r="F45" s="3">
-        <v>419700</v>
+        <v>728000</v>
       </c>
       <c r="G45" s="3">
-        <v>513400</v>
+        <v>700600</v>
       </c>
       <c r="H45" s="3">
-        <v>582400</v>
+        <v>754800</v>
       </c>
       <c r="I45" s="3">
-        <v>378100</v>
+        <v>485300</v>
       </c>
       <c r="J45" s="3">
-        <v>1167200</v>
+        <v>740500</v>
       </c>
       <c r="K45" s="3">
         <v>1025100</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>18320600</v>
+        <v>18305400</v>
       </c>
       <c r="E46" s="3">
-        <v>16243200</v>
+        <v>17348400</v>
       </c>
       <c r="F46" s="3">
-        <v>13258600</v>
+        <v>16215700</v>
       </c>
       <c r="G46" s="3">
-        <v>11633600</v>
+        <v>15876300</v>
       </c>
       <c r="H46" s="3">
-        <v>12204100</v>
+        <v>15816400</v>
       </c>
       <c r="I46" s="3">
-        <v>11640600</v>
+        <v>14943500</v>
       </c>
       <c r="J46" s="3">
-        <v>11419800</v>
+        <v>14343000</v>
       </c>
       <c r="K46" s="3">
         <v>10378800</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>11248000</v>
+        <v>1409400</v>
       </c>
       <c r="E47" s="3">
-        <v>10052100</v>
+        <v>1329900</v>
       </c>
       <c r="F47" s="3">
-        <v>8717500</v>
+        <v>1403000</v>
       </c>
       <c r="G47" s="3">
-        <v>6972500</v>
+        <v>1325800</v>
       </c>
       <c r="H47" s="3">
-        <v>6261500</v>
+        <v>1680800</v>
       </c>
       <c r="I47" s="3">
-        <v>5706200</v>
+        <v>1657100</v>
       </c>
       <c r="J47" s="3">
-        <v>6009700</v>
+        <v>1554800</v>
       </c>
       <c r="K47" s="3">
         <v>448900</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5162100</v>
+        <v>5157900</v>
       </c>
       <c r="E48" s="3">
-        <v>9148300</v>
+        <v>4885300</v>
       </c>
       <c r="F48" s="3">
-        <v>3523800</v>
+        <v>4310600</v>
       </c>
       <c r="G48" s="3">
-        <v>3015200</v>
+        <v>4114800</v>
       </c>
       <c r="H48" s="3">
-        <v>2878000</v>
+        <v>3729900</v>
       </c>
       <c r="I48" s="3">
-        <v>2343200</v>
+        <v>3008100</v>
       </c>
       <c r="J48" s="3">
-        <v>6941800</v>
+        <v>2967400</v>
       </c>
       <c r="K48" s="3">
         <v>2086500</v>
@@ -2354,25 +2354,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2362300</v>
+        <v>2219800</v>
       </c>
       <c r="E49" s="3">
-        <v>4528200</v>
+        <v>2246500</v>
       </c>
       <c r="F49" s="3">
-        <v>680800</v>
+        <v>653800</v>
       </c>
       <c r="G49" s="3">
-        <v>515000</v>
+        <v>518800</v>
       </c>
       <c r="H49" s="3">
-        <v>433000</v>
+        <v>405800</v>
       </c>
       <c r="I49" s="3">
-        <v>354600</v>
+        <v>368300</v>
       </c>
       <c r="J49" s="3">
-        <v>1006600</v>
+        <v>424400</v>
       </c>
       <c r="K49" s="3">
         <v>305800</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>957600</v>
+        <v>275100</v>
       </c>
       <c r="E52" s="3">
-        <v>698300</v>
+        <v>170800</v>
       </c>
       <c r="F52" s="3">
-        <v>612200</v>
+        <v>311000</v>
       </c>
       <c r="G52" s="3">
-        <v>507800</v>
+        <v>270100</v>
       </c>
       <c r="H52" s="3">
-        <v>512600</v>
+        <v>232000</v>
       </c>
       <c r="I52" s="3">
-        <v>514400</v>
+        <v>204200</v>
       </c>
       <c r="J52" s="3">
-        <v>6142500</v>
+        <v>217400</v>
       </c>
       <c r="K52" s="3">
         <v>4512600</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>38050700</v>
+        <v>38019100</v>
       </c>
       <c r="E54" s="3">
-        <v>33831900</v>
+        <v>36133700</v>
       </c>
       <c r="F54" s="3">
-        <v>26793000</v>
+        <v>32773800</v>
       </c>
       <c r="G54" s="3">
-        <v>22644200</v>
+        <v>30902100</v>
       </c>
       <c r="H54" s="3">
-        <v>22289200</v>
+        <v>28886700</v>
       </c>
       <c r="I54" s="3">
-        <v>20559200</v>
+        <v>26392500</v>
       </c>
       <c r="J54" s="3">
-        <v>20109800</v>
+        <v>25337900</v>
       </c>
       <c r="K54" s="3">
         <v>17732700</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2136400</v>
+        <v>2134600</v>
       </c>
       <c r="E57" s="3">
-        <v>6457900</v>
+        <v>3448600</v>
       </c>
       <c r="F57" s="3">
-        <v>2785600</v>
+        <v>3407500</v>
       </c>
       <c r="G57" s="3">
-        <v>2297600</v>
+        <v>3135500</v>
       </c>
       <c r="H57" s="3">
-        <v>2085800</v>
+        <v>2703200</v>
       </c>
       <c r="I57" s="3">
-        <v>2178000</v>
+        <v>2796000</v>
       </c>
       <c r="J57" s="3">
-        <v>4062900</v>
+        <v>2540200</v>
       </c>
       <c r="K57" s="3">
         <v>1698900</v>
@@ -2707,25 +2707,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4709400</v>
+        <v>4858600</v>
       </c>
       <c r="E58" s="3">
-        <v>9100600</v>
+        <v>5000500</v>
       </c>
       <c r="F58" s="3">
-        <v>3580800</v>
+        <v>4522500</v>
       </c>
       <c r="G58" s="3">
-        <v>2598900</v>
+        <v>3688800</v>
       </c>
       <c r="H58" s="3">
-        <v>2744400</v>
+        <v>3692700</v>
       </c>
       <c r="I58" s="3">
-        <v>2482600</v>
+        <v>3181500</v>
       </c>
       <c r="J58" s="3">
-        <v>7751800</v>
+        <v>3244400</v>
       </c>
       <c r="K58" s="3">
         <v>2251600</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3754900</v>
+        <v>3598700</v>
       </c>
       <c r="E59" s="3">
-        <v>3464100</v>
+        <v>3559200</v>
       </c>
       <c r="F59" s="3">
-        <v>2961200</v>
+        <v>3480200</v>
       </c>
       <c r="G59" s="3">
-        <v>2391100</v>
+        <v>3121000</v>
       </c>
       <c r="H59" s="3">
-        <v>2282200</v>
+        <v>2821700</v>
       </c>
       <c r="I59" s="3">
-        <v>1891500</v>
+        <v>2433600</v>
       </c>
       <c r="J59" s="3">
-        <v>4086200</v>
+        <v>1445900</v>
       </c>
       <c r="K59" s="3">
         <v>1604600</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10600700</v>
+        <v>10591900</v>
       </c>
       <c r="E60" s="3">
-        <v>11243400</v>
+        <v>12008300</v>
       </c>
       <c r="F60" s="3">
-        <v>9327500</v>
+        <v>11410100</v>
       </c>
       <c r="G60" s="3">
-        <v>7287600</v>
+        <v>9945300</v>
       </c>
       <c r="H60" s="3">
-        <v>7112400</v>
+        <v>9217600</v>
       </c>
       <c r="I60" s="3">
-        <v>6552000</v>
+        <v>8411100</v>
       </c>
       <c r="J60" s="3">
-        <v>6513900</v>
+        <v>8159700</v>
       </c>
       <c r="K60" s="3">
         <v>5555100</v>
@@ -2842,25 +2842,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>9421100</v>
+        <v>9671600</v>
       </c>
       <c r="E61" s="3">
-        <v>6888500</v>
+        <v>7613800</v>
       </c>
       <c r="F61" s="3">
-        <v>4190200</v>
+        <v>5395800</v>
       </c>
       <c r="G61" s="3">
-        <v>3609600</v>
+        <v>5192000</v>
       </c>
       <c r="H61" s="3">
-        <v>3666700</v>
+        <v>4991700</v>
       </c>
       <c r="I61" s="3">
-        <v>3490100</v>
+        <v>4485800</v>
       </c>
       <c r="J61" s="3">
-        <v>3354200</v>
+        <v>4210400</v>
       </c>
       <c r="K61" s="3">
         <v>3179900</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>874800</v>
+        <v>108000</v>
       </c>
       <c r="E62" s="3">
-        <v>772300</v>
+        <v>105900</v>
       </c>
       <c r="F62" s="3">
-        <v>600900</v>
+        <v>66100</v>
       </c>
       <c r="G62" s="3">
-        <v>570200</v>
+        <v>83500</v>
       </c>
       <c r="H62" s="3">
-        <v>595800</v>
+        <v>84000</v>
       </c>
       <c r="I62" s="3">
-        <v>389300</v>
+        <v>95100</v>
       </c>
       <c r="J62" s="3">
-        <v>1047600</v>
+        <v>254800</v>
       </c>
       <c r="K62" s="3">
         <v>552100</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>22602700</v>
+        <v>20879200</v>
       </c>
       <c r="E66" s="3">
-        <v>20523000</v>
+        <v>20190400</v>
       </c>
       <c r="F66" s="3">
-        <v>14878900</v>
+        <v>17270900</v>
       </c>
       <c r="G66" s="3">
-        <v>12164300</v>
+        <v>15649400</v>
       </c>
       <c r="H66" s="3">
-        <v>12045000</v>
+        <v>14741900</v>
       </c>
       <c r="I66" s="3">
-        <v>11046200</v>
+        <v>13391300</v>
       </c>
       <c r="J66" s="3">
-        <v>10943000</v>
+        <v>13037600</v>
       </c>
       <c r="K66" s="3">
         <v>9772900</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>12025100</v>
+        <v>12015200</v>
       </c>
       <c r="E72" s="3">
-        <v>10857700</v>
+        <v>11596400</v>
       </c>
       <c r="F72" s="3">
-        <v>10221400</v>
+        <v>12502900</v>
       </c>
       <c r="G72" s="3">
-        <v>9412900</v>
+        <v>12845700</v>
       </c>
       <c r="H72" s="3">
-        <v>8795700</v>
+        <v>11399100</v>
       </c>
       <c r="I72" s="3">
-        <v>8061300</v>
+        <v>10348600</v>
       </c>
       <c r="J72" s="3">
-        <v>14952500</v>
+        <v>9462200</v>
       </c>
       <c r="K72" s="3">
         <v>6513500</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>15448000</v>
+        <v>15435200</v>
       </c>
       <c r="E76" s="3">
-        <v>13308900</v>
+        <v>14214400</v>
       </c>
       <c r="F76" s="3">
-        <v>11914000</v>
+        <v>14573400</v>
       </c>
       <c r="G76" s="3">
-        <v>10479900</v>
+        <v>14301700</v>
       </c>
       <c r="H76" s="3">
-        <v>10244100</v>
+        <v>13276400</v>
       </c>
       <c r="I76" s="3">
-        <v>9512900</v>
+        <v>12212100</v>
       </c>
       <c r="J76" s="3">
-        <v>9166800</v>
+        <v>11553600</v>
       </c>
       <c r="K76" s="3">
         <v>7959800</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1693000</v>
+        <v>1691600</v>
       </c>
       <c r="E81" s="3">
-        <v>1111000</v>
+        <v>1186500</v>
       </c>
       <c r="F81" s="3">
-        <v>1240800</v>
+        <v>1525400</v>
       </c>
       <c r="G81" s="3">
-        <v>912500</v>
+        <v>1245300</v>
       </c>
       <c r="H81" s="3">
-        <v>1058300</v>
+        <v>1371600</v>
       </c>
       <c r="I81" s="3">
-        <v>984000</v>
+        <v>1263200</v>
       </c>
       <c r="J81" s="3">
-        <v>906100</v>
+        <v>1211400</v>
       </c>
       <c r="K81" s="3">
         <v>879700</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>761600</v>
+        <v>588600</v>
       </c>
       <c r="E83" s="3">
-        <v>605000</v>
+        <v>523900</v>
       </c>
       <c r="F83" s="3">
-        <v>509100</v>
+        <v>501500</v>
       </c>
       <c r="G83" s="3">
-        <v>478100</v>
+        <v>537800</v>
       </c>
       <c r="H83" s="3">
-        <v>441900</v>
+        <v>475900</v>
       </c>
       <c r="I83" s="3">
-        <v>352300</v>
+        <v>374800</v>
       </c>
       <c r="J83" s="3">
-        <v>320500</v>
+        <v>340100</v>
       </c>
       <c r="K83" s="3">
         <v>288000</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-122600</v>
+        <v>-122500</v>
       </c>
       <c r="E89" s="3">
-        <v>-54500</v>
+        <v>-58200</v>
       </c>
       <c r="F89" s="3">
-        <v>656800</v>
+        <v>803500</v>
       </c>
       <c r="G89" s="3">
-        <v>1014700</v>
+        <v>1384800</v>
       </c>
       <c r="H89" s="3">
-        <v>585100</v>
+        <v>758300</v>
       </c>
       <c r="I89" s="3">
-        <v>633000</v>
+        <v>812500</v>
       </c>
       <c r="J89" s="3">
-        <v>974000</v>
+        <v>1973500</v>
       </c>
       <c r="K89" s="3">
         <v>1228300</v>
@@ -4029,25 +4029,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1064200</v>
+        <v>-1063300</v>
       </c>
       <c r="E91" s="3">
-        <v>-955400</v>
+        <v>-1020400</v>
       </c>
       <c r="F91" s="3">
-        <v>-691800</v>
+        <v>-846200</v>
       </c>
       <c r="G91" s="3">
-        <v>-432500</v>
+        <v>-590200</v>
       </c>
       <c r="H91" s="3">
-        <v>-541300</v>
+        <v>-701600</v>
       </c>
       <c r="I91" s="3">
-        <v>-450100</v>
+        <v>-465200</v>
       </c>
       <c r="J91" s="3">
-        <v>-872400</v>
+        <v>-571800</v>
       </c>
       <c r="K91" s="3">
         <v>-372800</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1231400</v>
+        <v>-1230400</v>
       </c>
       <c r="E94" s="3">
-        <v>-2261300</v>
+        <v>-2415200</v>
       </c>
       <c r="F94" s="3">
-        <v>-904300</v>
+        <v>-1106200</v>
       </c>
       <c r="G94" s="3">
-        <v>-334600</v>
+        <v>-456700</v>
       </c>
       <c r="H94" s="3">
-        <v>-649400</v>
+        <v>-841700</v>
       </c>
       <c r="I94" s="3">
-        <v>-417200</v>
+        <v>-535500</v>
       </c>
       <c r="J94" s="3">
-        <v>-326500</v>
+        <v>-1157200</v>
       </c>
       <c r="K94" s="3">
         <v>-1112400</v>
@@ -4228,25 +4228,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-386800</v>
+        <v>386500</v>
       </c>
       <c r="E96" s="3">
-        <v>-365400</v>
+        <v>390300</v>
       </c>
       <c r="F96" s="3">
-        <v>-343200</v>
+        <v>419800</v>
       </c>
       <c r="G96" s="3">
-        <v>-311400</v>
+        <v>424900</v>
       </c>
       <c r="H96" s="3">
-        <v>-305800</v>
+        <v>396300</v>
       </c>
       <c r="I96" s="3">
-        <v>-288900</v>
+        <v>370900</v>
       </c>
       <c r="J96" s="3">
-        <v>-272800</v>
+        <v>341100</v>
       </c>
       <c r="K96" s="3">
         <v>-231300</v>
@@ -4408,25 +4408,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1266700</v>
+        <v>1265600</v>
       </c>
       <c r="E100" s="3">
-        <v>2006200</v>
+        <v>2142600</v>
       </c>
       <c r="F100" s="3">
-        <v>430200</v>
+        <v>526200</v>
       </c>
       <c r="G100" s="3">
-        <v>-485300</v>
+        <v>-662300</v>
       </c>
       <c r="H100" s="3">
-        <v>-152800</v>
+        <v>-198000</v>
       </c>
       <c r="I100" s="3">
-        <v>-197500</v>
+        <v>-253500</v>
       </c>
       <c r="J100" s="3">
-        <v>-231300</v>
+        <v>-289200</v>
       </c>
       <c r="K100" s="3">
         <v>75500</v>
@@ -4453,25 +4453,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>61300</v>
+        <v>61200</v>
       </c>
       <c r="E101" s="3">
-        <v>76600</v>
+        <v>81800</v>
       </c>
       <c r="F101" s="3">
-        <v>71000</v>
+        <v>86800</v>
       </c>
       <c r="G101" s="3">
-        <v>-29700</v>
+        <v>-40500</v>
       </c>
       <c r="H101" s="3">
-        <v>7900</v>
+        <v>10300</v>
       </c>
       <c r="I101" s="3">
-        <v>-29600</v>
+        <v>-38000</v>
       </c>
       <c r="J101" s="3">
-        <v>19000</v>
+        <v>17100</v>
       </c>
       <c r="K101" s="3">
         <v>-37800</v>
@@ -4501,22 +4501,22 @@
         <v>-26100</v>
       </c>
       <c r="E102" s="3">
-        <v>-233200</v>
+        <v>-249000</v>
       </c>
       <c r="F102" s="3">
-        <v>253600</v>
+        <v>310200</v>
       </c>
       <c r="G102" s="3">
-        <v>165100</v>
+        <v>225300</v>
       </c>
       <c r="H102" s="3">
-        <v>-209200</v>
+        <v>-271100</v>
       </c>
       <c r="I102" s="3">
-        <v>-11300</v>
+        <v>-14600</v>
       </c>
       <c r="J102" s="3">
-        <v>435300</v>
+        <v>544300</v>
       </c>
       <c r="K102" s="3">
         <v>153600</v>

--- a/AAII_Financials/Yearly/KUBTY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KUBTY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>KUBTY</t>
   </si>
@@ -656,208 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42094</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41729</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41364</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40999</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>19185100</v>
+      </c>
+      <c r="E8" s="3">
         <v>21429300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20299700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>19079400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>17956500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>17667400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16864700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15550500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10598000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8825500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13980900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14497500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10613700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8941100</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13282700</v>
+      </c>
+      <c r="E9" s="3">
         <v>15211500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15100100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13592000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12774200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12515200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12057900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11015300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7453700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6015100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9732900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10157800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7709700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6526900</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5902400</v>
+      </c>
+      <c r="E10" s="3">
         <v>6217800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5199500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5487400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5182300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5152200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4806900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4535300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3144300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2810300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4248000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4339800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2904100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2414300</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -875,34 +887,35 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>710200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>669900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>567000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>536200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>488700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>490700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>427100</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,81 +980,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>-46200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>42200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>25400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>14600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>40000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-65700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>31900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-6500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>15600</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>22800</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>766200</v>
+      </c>
+      <c r="E15" s="3">
         <v>486000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>428100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>382200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>408700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>366400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>397100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>402100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1051,12 +1073,15 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17177500</v>
+      </c>
+      <c r="E17" s="3">
         <v>19080700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18722900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16975100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16202200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15741100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15067400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13776400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9344600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7642300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12182400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12552200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9585100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8026500</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2007600</v>
+      </c>
+      <c r="E18" s="3">
         <v>2348600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1576800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2104400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1754300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1926300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1797300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1774100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1253500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1183100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1798500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1945400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1028600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>914600</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,233 +1212,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E20" s="3">
         <v>30100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-186600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-109200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-33600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>34600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-91600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>57700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>23600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>73100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>99600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>78000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2806200</v>
+      </c>
+      <c r="E21" s="3">
         <v>2804600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2191400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2595700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2196600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2291400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2159900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2267900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1597900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1419800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2209300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2383900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1373100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1124200</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E22" s="3">
         <v>31300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>10100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>85800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>10400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>14400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>16800</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2165100</v>
+      </c>
+      <c r="E23" s="3">
         <v>2443200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1765300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2220000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1825700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1951600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1816200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1911200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1307900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1201800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1861200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2030500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1095000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>895300</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>513500</v>
+      </c>
+      <c r="E24" s="3">
         <v>598800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>442500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>563400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>455700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>487700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>447700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>620800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>375500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>384700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>539200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>691100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>370300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>324200</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1651600</v>
+      </c>
+      <c r="E26" s="3">
         <v>1844500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1322800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1656600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1370100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1463900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1368500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1290400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>932400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>817100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1322000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1339400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>724700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>571100</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1465700</v>
+      </c>
+      <c r="E27" s="3">
         <v>1691600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1186500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1525400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1245300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1371600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1263200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1211400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>879700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>780700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1233500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1265300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>669800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>546000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1611,8 +1671,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,99 +1785,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-30100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>186600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>109200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>33600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-34600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>91600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-57700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-23600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-73100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-99600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-78000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2500</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1465700</v>
+      </c>
+      <c r="E33" s="3">
         <v>1691600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1186500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1525400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1245300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1371600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1263200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1211400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>879700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>780700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1233500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1265300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>669800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>546000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1465700</v>
+      </c>
+      <c r="E35" s="3">
         <v>1691600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1186500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1525400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1245300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1371600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1263200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1211400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>879700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>780700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1233500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1265300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>669800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>546000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42094</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41729</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41364</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40999</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,413 +2073,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1877200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1575700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1712200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2246300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2159900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1837200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2088300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2048400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1124900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1037200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>995700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>836300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1004800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>892000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>588900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>542300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>441900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>484100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>662200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>495600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>40500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>53800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>80100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>44500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>38800</v>
       </c>
-      <c r="P42" s="3" t="s">
+      <c r="Q42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10429500</v>
+      </c>
+      <c r="E43" s="3">
         <v>11005400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9788000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8369500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8907900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9043500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8495500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8120700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5823300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6038400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7816300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7348700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5510400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4425400</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4403200</v>
+      </c>
+      <c r="E44" s="3">
         <v>4739200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4887100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4430000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3623800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3518700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3378700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3218500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2365000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5054300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2978100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2880700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2104200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1792400</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1528600</v>
+      </c>
+      <c r="E45" s="3">
         <v>396200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>418800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>728000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>700600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>754800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>485300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>740500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1025100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1880900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>842800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>748200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>565200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>571800</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18238500</v>
+      </c>
+      <c r="E46" s="3">
         <v>18305400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17348400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16215700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15876300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15816400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14943500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14343000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10378800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10570100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12713000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11858400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9223400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7681500</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>11682500</v>
+      </c>
+      <c r="E47" s="3">
         <v>1409400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1329900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1403000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1325800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1680800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1657100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1554800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>448900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>629500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>543000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>555400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>460200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2873400</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5481700</v>
+      </c>
+      <c r="E48" s="3">
         <v>5157900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4885300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4310600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4114800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3729900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3008100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2967400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2086500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2026800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2617400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2716800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2322700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1996300</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2208300</v>
+      </c>
+      <c r="E49" s="3">
         <v>2219800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2246500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>653800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>518800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>405800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>368300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>424400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>305800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>417300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>305700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>332800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>262700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>238600</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,54 +2598,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3">
         <v>275100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>170800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>311000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>270100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>232000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>204200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>217400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4512600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4710600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5641700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4762500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3580900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>405700</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>38281800</v>
+      </c>
+      <c r="E54" s="3">
         <v>38019100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36133700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>32773800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30902100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28886700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>26392500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>25337900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17732700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17958400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21820800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>20225800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15850000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13195600</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,278 +2785,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1747500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2134600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3448600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3407500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3135500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2703200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2796000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2540200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1698900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1845800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2011600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2313200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2209100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1765800</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5744500</v>
+      </c>
+      <c r="E58" s="3">
         <v>4858600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5000500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4522500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3688800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3692700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3181500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3244400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2251600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2441300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2534100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2607600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1701300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1718500</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3787400</v>
+      </c>
+      <c r="E59" s="3">
         <v>3598700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3559200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3480200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3121000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2821700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2433600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1445900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1604600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1480200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1887400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1988100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1496900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1269900</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11279300</v>
+      </c>
+      <c r="E60" s="3">
         <v>10591900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12008300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11410100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9945300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9217600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8411100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8159700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5555100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5728000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6433100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6908900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5407200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4754200</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8745300</v>
+      </c>
+      <c r="E61" s="3">
         <v>9671600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7613800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5395800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5192000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4991700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4485800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4210400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3179900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3008800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4228400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3032900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2484800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1635600</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>376300</v>
+      </c>
+      <c r="E62" s="3">
         <v>108000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>105900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>66100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>83500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>84000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>95100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>254800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>552100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>582100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>768900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>668100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>589500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>532800</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20855500</v>
+      </c>
+      <c r="E66" s="3">
         <v>20879200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>20190400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17270900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15649400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14741900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13391300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13037600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9772900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9873600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12121000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11242200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8955100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7401000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11654700</v>
+      </c>
+      <c r="E72" s="3">
         <v>12015200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>11596400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12502900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12845700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11399100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10348600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9462200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6513500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6305200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7207300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6950700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5587500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5146800</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15757000</v>
+      </c>
+      <c r="E76" s="3">
         <v>15435200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14214400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14573400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14301700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13276400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12212100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11553600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7959800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8084800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9699800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8983500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6894900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5794600</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42094</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41729</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41364</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40999</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1465700</v>
+      </c>
+      <c r="E81" s="3">
         <v>1691600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1186500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1525400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1245300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1371600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1263200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1211400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>879700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>780700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1233500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1265300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>669800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>546000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,53 +3886,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>766200</v>
+      </c>
+      <c r="E83" s="3">
         <v>588600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>523900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>501500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>537800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>475900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>374800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>340100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>288000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>221200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>336900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>339700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>265900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>212100</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1794200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-122500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-58200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>803500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1384800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>758300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>812500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1973500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1228300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1397000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>740000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>800700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>463400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>708700</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1152300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1063300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1020400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-846200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-590200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-701600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-465200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-571800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-372800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-278400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-411300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-510800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-424000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-239200</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,54 +4383,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1328600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1230400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2415200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1106200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-456700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-841700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-535500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1157200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1112400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-923900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1035200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1001400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-629400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-620300</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,53 +4454,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>386500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>390300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>419800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>424900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>396300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>370900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>341100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-231300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-264900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-330400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-229400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-182700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-157000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,142 +4643,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-167100</v>
+      </c>
+      <c r="E100" s="3">
         <v>1265600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2142600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>526200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-662300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-198000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-253500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-289200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>75500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-196200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>463400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>30900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>196800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-117700</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>165900</v>
+      </c>
+      <c r="E101" s="3">
         <v>61200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>81800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>86800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-40500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>10300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-38000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>17100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-37800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-36900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>60800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>47100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>59800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>464400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-26100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-249000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>310200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>225300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-271100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-14600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>544300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>153600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>240100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>229000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-122700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>90700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-42000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/KUBTY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KUBTY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>KUBTY</t>
   </si>
@@ -893,8 +893,8 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>711600</v>
       </c>
       <c r="E12" s="3">
         <v>710200</v>
@@ -989,8 +989,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-91600</v>
       </c>
       <c r="E14" s="3">
         <v>-46200</v>
@@ -1038,7 +1038,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>766200</v>
+        <v>502900</v>
       </c>
       <c r="E15" s="3">
         <v>486000</v>
@@ -1103,7 +1103,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>17177500</v>
+        <v>17122200</v>
       </c>
       <c r="E17" s="3">
         <v>19080700</v>
@@ -1151,7 +1151,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2007600</v>
+        <v>2062900</v>
       </c>
       <c r="E18" s="3">
         <v>2348600</v>
@@ -1219,7 +1219,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-32400</v>
+        <v>101700</v>
       </c>
       <c r="E20" s="3">
         <v>30100</v>
@@ -1267,7 +1267,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2806200</v>
+        <v>2464100</v>
       </c>
       <c r="E21" s="3">
         <v>2804600</v>
@@ -1315,7 +1315,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>42300</v>
+        <v>33100</v>
       </c>
       <c r="E22" s="3">
         <v>31300</v>
@@ -1795,7 +1795,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>32400</v>
+        <v>-101700</v>
       </c>
       <c r="E32" s="3">
         <v>-30100</v>
@@ -2128,7 +2128,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>660200</v>
       </c>
       <c r="E42" s="3">
         <v>588900</v>
@@ -2176,7 +2176,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>10429500</v>
+        <v>10744800</v>
       </c>
       <c r="E43" s="3">
         <v>11005400</v>
@@ -2272,7 +2272,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1528600</v>
+        <v>553200</v>
       </c>
       <c r="E45" s="3">
         <v>396200</v>
@@ -2368,7 +2368,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>11682500</v>
+        <v>1327500</v>
       </c>
       <c r="E47" s="3">
         <v>1409400</v>
@@ -2464,7 +2464,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2208300</v>
+        <v>2096900</v>
       </c>
       <c r="E49" s="3">
         <v>2219800</v>
@@ -2607,8 +2607,8 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
+      <c r="D52" s="3">
+        <v>267800</v>
       </c>
       <c r="E52" s="3">
         <v>275100</v>
@@ -2840,7 +2840,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5744500</v>
+        <v>5893800</v>
       </c>
       <c r="E58" s="3">
         <v>4858600</v>
@@ -2888,7 +2888,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3787400</v>
+        <v>3650900</v>
       </c>
       <c r="E59" s="3">
         <v>3598700</v>
@@ -2936,7 +2936,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>11279300</v>
+        <v>11292200</v>
       </c>
       <c r="E60" s="3">
         <v>10591900</v>
@@ -2984,7 +2984,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8745300</v>
+        <v>9007600</v>
       </c>
       <c r="E61" s="3">
         <v>9671600</v>
@@ -3032,7 +3032,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>376300</v>
+        <v>101100</v>
       </c>
       <c r="E62" s="3">
         <v>108000</v>
@@ -3893,7 +3893,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>766200</v>
+        <v>605300</v>
       </c>
       <c r="E83" s="3">
         <v>588600</v>
@@ -4461,7 +4461,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>366300</v>
       </c>
       <c r="E96" s="3">
         <v>386500</v>

--- a/AAII_Financials/Yearly/KUBTY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KUBTY_YR_FIN.xlsx
@@ -656,220 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>19254600</v>
+      </c>
+      <c r="E8" s="3">
         <v>19185100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>21429300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20299700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>19079400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>17956500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>17667400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16864700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15550500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10598000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8825500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13980900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14497500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10613700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8941100</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13614400</v>
+      </c>
+      <c r="E9" s="3">
         <v>13282700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15211500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15100100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13592000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12774200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12515200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12057900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11015300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7453700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6015100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9732900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10157800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7709700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6526900</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5640200</v>
+      </c>
+      <c r="E10" s="3">
         <v>5902400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6217800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5199500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5487400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5182300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5152200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4806900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4535300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3144300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2810300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4248000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4339800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2904100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2414300</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -888,37 +900,38 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>694700</v>
+      </c>
+      <c r="E12" s="3">
         <v>711600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>710200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>669900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>567000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>536200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>488700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>490700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>427100</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -935,9 +948,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,87 +999,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-128000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-91600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-46200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>42200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>25400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>14600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>40000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-65700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>31900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-6500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>15600</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>22800</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>540200</v>
+      </c>
+      <c r="E15" s="3">
         <v>502900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>486000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>428100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>382200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>408700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>366400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>397100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>402100</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1076,12 +1098,15 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3" t="s">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17544500</v>
+      </c>
+      <c r="E17" s="3">
         <v>17122200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>19080700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18722900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16975100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16202200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15741100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15067400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13776400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9344600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7642300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12182400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12552200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9585100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8026500</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1710100</v>
+      </c>
+      <c r="E18" s="3">
         <v>2062900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2348600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1576800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2104400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1754300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1926300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1797300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1774100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1253500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1183100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1798500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1945400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1028600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>914600</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,248 +1245,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>119800</v>
+      </c>
+      <c r="E20" s="3">
         <v>101700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>30100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-186600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-109200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-33600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>34600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-91600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>57700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>23600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>73100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>99600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>78000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2500</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2130400</v>
+      </c>
+      <c r="E21" s="3">
         <v>2464100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2804600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2191400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2595700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2196600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2291400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2159900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2267900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1597900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1419800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2209300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2383900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1373100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1124200</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E22" s="3">
         <v>33100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>31300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>8600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>85800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>10400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>14400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>16800</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1817000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2165100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2443200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1765300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2220000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1825700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1951600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1816200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1911200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1307900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1201800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1861200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2030500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1095000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>895300</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>434500</v>
+      </c>
+      <c r="E24" s="3">
         <v>513500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>598800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>442500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>563400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>455700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>487700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>447700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>620800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>375500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>384700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>539200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>691100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>370300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>324200</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1382500</v>
+      </c>
+      <c r="E26" s="3">
         <v>1651600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1844500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1322800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1656600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1370100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1463900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1368500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1290400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>932400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>817100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1322000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1339400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>724700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>571100</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1190700</v>
+      </c>
+      <c r="E27" s="3">
         <v>1465700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1691600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1186500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1525400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1245300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1371600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1263200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1211400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>879700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>780700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1233500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1265300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>669800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>546000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1674,8 +1734,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1692,9 +1752,12 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-119800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-101700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-30100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>186600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>109200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>33600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-34600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>91600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-57700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-23600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-73100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-99600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-78000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2500</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1190700</v>
+      </c>
+      <c r="E33" s="3">
         <v>1465700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1691600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1186500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1525400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1245300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1371600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1263200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1211400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>879700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>780700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1233500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1265300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>669800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>546000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1190700</v>
+      </c>
+      <c r="E35" s="3">
         <v>1465700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1691600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1186500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1525400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1245300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1371600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1263200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1211400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>879700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>780700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1233500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1265300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>669800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>546000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,440 +2159,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1766500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1877200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1575700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1712200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2246300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2159900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1837200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2088300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2048400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1124900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1037200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>995700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>836300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1004800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>892000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1017900</v>
+      </c>
+      <c r="E42" s="3">
         <v>660200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>588900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>542300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>441900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>484100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>662200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>495600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>40500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>53800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>80100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>44500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>38800</v>
       </c>
-      <c r="Q42" s="3" t="s">
+      <c r="R42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10982800</v>
+      </c>
+      <c r="E43" s="3">
         <v>10744800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11005400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9788000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8369500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8907900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9043500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8495500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8120700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5823300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6038400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7816300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7348700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5510400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4425400</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4393800</v>
+      </c>
+      <c r="E44" s="3">
         <v>4403200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4739200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4887100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4430000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3623800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3518700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3378700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3218500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2365000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5054300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2978100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2880700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2104200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1792400</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>483200</v>
+      </c>
+      <c r="E45" s="3">
         <v>553200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>396200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>418800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>728000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>700600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>754800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>485300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>740500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1025100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1880900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>842800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>748200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>565200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>571800</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18644200</v>
+      </c>
+      <c r="E46" s="3">
         <v>18238500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18305400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17348400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16215700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15876300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15816400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14943500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14343000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10378800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10570100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12713000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11858400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9223400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7681500</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1269800</v>
+      </c>
+      <c r="E47" s="3">
         <v>1327500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1409400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1329900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1403000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1325800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1680800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1657100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1554800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>448900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>629500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>543000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>555400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>460200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2873400</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5997800</v>
+      </c>
+      <c r="E48" s="3">
         <v>5481700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5157900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4885300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4310600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4114800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3729900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3008100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2967400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2086500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2026800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2617400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2716800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2322700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1996300</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2094700</v>
+      </c>
+      <c r="E49" s="3">
         <v>2096900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2219800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2418100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>653800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>518800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>405800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>368300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>424400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>305800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>417300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>305700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>332800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>262700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>238600</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,57 +2717,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>455700</v>
+      </c>
+      <c r="E52" s="3">
         <v>267800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>275100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>170800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>311000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>270100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>232000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>204200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>217400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4512600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4710600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5641700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4762500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3580900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>405700</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>39575200</v>
+      </c>
+      <c r="E54" s="3">
         <v>38281800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>38019100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>36133700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>32773800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>30902100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>28886700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>26392500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25337900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17732700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17958400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21820800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>20225800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15850000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13195600</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,296 +2915,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1890300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1747500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2134600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3448600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3407500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3135500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2703200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2796000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2540200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1698900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1845800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2011600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2313200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2209100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1765800</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5644700</v>
+      </c>
+      <c r="E58" s="3">
         <v>5893800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4858600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5000500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4522500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3688800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3692700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3181500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3244400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2251600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2441300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2534100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2607600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1701300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1718500</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3760000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3650900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3598700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3559200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3480200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3121000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2821700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2433600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1445900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1604600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1480200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1887400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1988100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1496900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1269900</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11295000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11292200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10591900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12008300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11410100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9945300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9217600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8411100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8159700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5555100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5728000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6433100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6908900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5407200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4754200</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9186900</v>
+      </c>
+      <c r="E61" s="3">
         <v>9007600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9671600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7613800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5395800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5192000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4991700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4485800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4210400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3179900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3008800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4228400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3032900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2484800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1635600</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>117000</v>
+      </c>
+      <c r="E62" s="3">
         <v>101100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>108000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>105900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>66100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>83500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>84000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>95100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>254800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>552100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>582100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>768900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>668100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>589500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>532800</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21250900</v>
+      </c>
+      <c r="E66" s="3">
         <v>20855500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>20879200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20190400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17270900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15649400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14741900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13391300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13037600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9772900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9873600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12121000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11242200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8955100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7401000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12474700</v>
+      </c>
+      <c r="E72" s="3">
         <v>11654700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>12015200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11596400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12502900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>12845700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11399100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10348600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9462200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6513500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6305200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7207300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6950700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5587500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5146800</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16729500</v>
+      </c>
+      <c r="E76" s="3">
         <v>15757000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15435200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14214400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14573400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14301700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13276400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12212100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11553600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7959800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8084800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9699800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8983500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6894900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5794600</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1190700</v>
+      </c>
+      <c r="E81" s="3">
         <v>1465700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1691600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1186500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1525400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1245300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1371600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1263200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1211400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>879700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>780700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1233500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1265300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>669800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>546000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>657300</v>
+      </c>
+      <c r="E83" s="3">
         <v>605300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>588600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>523900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>501500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>537800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>475900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>374800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>340100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>288000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>221200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>336900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>339700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>265900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>212100</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2091400</v>
+      </c>
+      <c r="E89" s="3">
         <v>1794200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-122500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-58200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>803500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1384800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>758300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>812500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1973500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1228300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1397000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>740000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>800700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>463400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>708700</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-975900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1152300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1063300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1020400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-846200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-590200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-701600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-465200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-571800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-372800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-278400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-411300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-510800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-424000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-239200</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1044300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1328600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1230400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2415200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1106200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-456700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-841700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-535500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1157200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1112400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-923900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1035200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1001400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-629400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-620300</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,56 +4687,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>364700</v>
+      </c>
+      <c r="E96" s="3">
         <v>366300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>386500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>390300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>419800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>424900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>396300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>370900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>341100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-231300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-264900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-330400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-229400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-182700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-157000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,151 +4888,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1176500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-167100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1265600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2142600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>526200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-662300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-198000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-253500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-289200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>75500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-196200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>463400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>30900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>196800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-117700</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E101" s="3">
         <v>165900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>61200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>81800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>86800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-40500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>10300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-38000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>17100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-37800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-36900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>60800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>47100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>59800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-12700</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-115900</v>
+      </c>
+      <c r="E102" s="3">
         <v>464400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-26100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-249000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>310200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>225300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-271100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-14600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>544300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>153600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>240100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>229000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-122700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>90700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-42000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
